--- a/Tomoscan_pso_interlaced/risultati_golden_N32_K4_PSO20000.xlsx
+++ b/Tomoscan_pso_interlaced/risultati_golden_N32_K4_PSO20000.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="MOD360" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UNWRAPPED" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="COUNTS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DELTA_THETA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UNWRAPPED_ACQ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="COUNTS_PSO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DELTA_THETA_PSO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_mod360</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -457,576 +457,576 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794608</v>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08</v>
+        <v>7.668</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.005310586853381594</v>
+        <v>0.00495494920539219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.742188968180672</v>
+        <v>20.06211240030279</v>
       </c>
       <c r="B4" t="n">
-        <v>375</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>6.75</v>
+        <v>20.07</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007811031819327852</v>
+        <v>0.007887599697205872</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.663045050794608</v>
+        <v>27.7251574510974</v>
       </c>
       <c r="B5" t="n">
-        <v>426</v>
+        <v>1540</v>
       </c>
       <c r="C5" t="n">
-        <v>7.668</v>
+        <v>27.72</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00495494920539219</v>
+        <v>-0.005157451097403509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.82749955503408</v>
+        <v>40.12422480060559</v>
       </c>
       <c r="B6" t="n">
-        <v>435</v>
+        <v>2229</v>
       </c>
       <c r="C6" t="n">
-        <v>7.83</v>
+        <v>40.122</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002500444965919613</v>
+        <v>-0.002224800605588939</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.48437793636134</v>
+        <v>52.52329215011355</v>
       </c>
       <c r="B7" t="n">
-        <v>749</v>
+        <v>2918</v>
       </c>
       <c r="C7" t="n">
-        <v>13.482</v>
+        <v>52.524</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002377936361344979</v>
+        <v>0.0007078498864530047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14.40523401897528</v>
+        <v>60.18633720090838</v>
       </c>
       <c r="B8" t="n">
-        <v>800</v>
+        <v>3344</v>
       </c>
       <c r="C8" t="n">
-        <v>14.4</v>
+        <v>60.192</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.005234018975279753</v>
+        <v>0.005662799091616932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20.06211240030279</v>
+        <v>72.58540455041634</v>
       </c>
       <c r="B9" t="n">
-        <v>1115</v>
+        <v>4033</v>
       </c>
       <c r="C9" t="n">
-        <v>20.07</v>
+        <v>72.59399999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007887599697205872</v>
+        <v>0.008595449583651771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20.22656690454201</v>
+        <v>92.64751695071936</v>
       </c>
       <c r="B10" t="n">
-        <v>1124</v>
+        <v>5147</v>
       </c>
       <c r="C10" t="n">
-        <v>20.232</v>
+        <v>92.646</v>
       </c>
       <c r="D10" t="n">
-        <v>0.005433095457984649</v>
+        <v>-0.001516950719363308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21.14742298715595</v>
+        <v>105.0465843002271</v>
       </c>
       <c r="B11" t="n">
-        <v>1175</v>
+        <v>5836</v>
       </c>
       <c r="C11" t="n">
-        <v>21.15</v>
+        <v>105.048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002577012844046322</v>
+        <v>0.001415699772906009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26.80430136848346</v>
+        <v>112.7096293510222</v>
       </c>
       <c r="B12" t="n">
-        <v>1489</v>
+        <v>6262</v>
       </c>
       <c r="C12" t="n">
-        <v>26.802</v>
+        <v>112.716</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.002301368483465183</v>
+        <v>0.006370648977835458</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27.7251574510974</v>
+        <v>125.1086967005299</v>
       </c>
       <c r="B13" t="n">
-        <v>1540</v>
+        <v>6950</v>
       </c>
       <c r="C13" t="n">
-        <v>27.72</v>
+        <v>125.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.005157451097403509</v>
+        <v>-0.008696700529895907</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27.88961195533662</v>
+        <v>137.5077640500378</v>
       </c>
       <c r="B14" t="n">
-        <v>1549</v>
+        <v>7639</v>
       </c>
       <c r="C14" t="n">
-        <v>27.882</v>
+        <v>137.502</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.007611955336624732</v>
+        <v>-0.005764050037839752</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33.54649033666414</v>
+        <v>145.1708091008327</v>
       </c>
       <c r="B15" t="n">
-        <v>1864</v>
+        <v>8065</v>
       </c>
       <c r="C15" t="n">
-        <v>33.552</v>
+        <v>145.17</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005509663335864445</v>
+        <v>-0.0008091008326971405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>34.46734641927807</v>
+        <v>157.5698764503406</v>
       </c>
       <c r="B16" t="n">
-        <v>1915</v>
+        <v>8754</v>
       </c>
       <c r="C16" t="n">
-        <v>34.47</v>
+        <v>157.572</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002653580721926119</v>
+        <v>0.002123549659359014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40.12422480060559</v>
+        <v>165.2329215011359</v>
       </c>
       <c r="B17" t="n">
-        <v>2229</v>
+        <v>9180</v>
       </c>
       <c r="C17" t="n">
-        <v>40.122</v>
+        <v>165.24</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002224800605588939</v>
+        <v>0.0070784988640753</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40.28867930484481</v>
+        <v>177.6319888506432</v>
       </c>
       <c r="B18" t="n">
-        <v>2238</v>
+        <v>9868</v>
       </c>
       <c r="C18" t="n">
-        <v>40.284</v>
+        <v>177.624</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004679304844806609</v>
+        <v>-0.007988850643215528</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41.20953538745874</v>
+        <v>190.0310562001514</v>
       </c>
       <c r="B19" t="n">
-        <v>2289</v>
+        <v>10557</v>
       </c>
       <c r="C19" t="n">
-        <v>41.202</v>
+        <v>190.026</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.007535387458744935</v>
+        <v>-0.005056200151415169</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.86641376878626</v>
+        <v>197.694101250946</v>
       </c>
       <c r="B20" t="n">
-        <v>2604</v>
+        <v>10983</v>
       </c>
       <c r="C20" t="n">
-        <v>46.872</v>
+        <v>197.694</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005586231213740689</v>
+        <v>-0.0001012509460167621</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47.95172435563941</v>
+        <v>210.0931686004542</v>
       </c>
       <c r="B21" t="n">
-        <v>2664</v>
+        <v>11672</v>
       </c>
       <c r="C21" t="n">
-        <v>47.952</v>
+        <v>210.096</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002756443605846925</v>
+        <v>0.002831399545812019</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52.52329215011355</v>
+        <v>230.155281000757</v>
       </c>
       <c r="B22" t="n">
-        <v>2918</v>
+        <v>12786</v>
       </c>
       <c r="C22" t="n">
-        <v>52.524</v>
+        <v>230.148</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0007078498864530047</v>
+        <v>-0.007281000756989897</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53.60860273696693</v>
+        <v>242.5543483502649</v>
       </c>
       <c r="B23" t="n">
-        <v>2978</v>
+        <v>13475</v>
       </c>
       <c r="C23" t="n">
-        <v>53.604</v>
+        <v>242.55</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.004602736966930365</v>
+        <v>-0.004348350264962164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59.26548111829422</v>
+        <v>250.2173934010598</v>
       </c>
       <c r="B24" t="n">
-        <v>3293</v>
+        <v>13901</v>
       </c>
       <c r="C24" t="n">
-        <v>59.274</v>
+        <v>250.218</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008518881705782633</v>
+        <v>0.000606598940208869</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60.18633720090838</v>
+        <v>262.616460750568</v>
       </c>
       <c r="B25" t="n">
-        <v>3344</v>
+        <v>14590</v>
       </c>
       <c r="C25" t="n">
-        <v>60.192</v>
+        <v>262.62</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005662799091616932</v>
+        <v>0.00353924943203765</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60.3507917051476</v>
+        <v>275.0155281000757</v>
       </c>
       <c r="B26" t="n">
-        <v>3353</v>
+        <v>15279</v>
       </c>
       <c r="C26" t="n">
-        <v>60.354</v>
+        <v>275.022</v>
       </c>
       <c r="D26" t="n">
-        <v>0.003208294852399263</v>
+        <v>0.006471899924292757</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66.00767008647489</v>
+        <v>282.6785731508708</v>
       </c>
       <c r="B27" t="n">
-        <v>3667</v>
+        <v>15704</v>
       </c>
       <c r="C27" t="n">
-        <v>66.006</v>
+        <v>282.672</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.001670086474888421</v>
+        <v>-0.006573150870792688</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66.92852616908905</v>
+        <v>295.0776405003785</v>
       </c>
       <c r="B28" t="n">
-        <v>3718</v>
+        <v>16393</v>
       </c>
       <c r="C28" t="n">
-        <v>66.92399999999999</v>
+        <v>295.074</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.004526169089061227</v>
+        <v>-0.003640500378480738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72.58540455041634</v>
+        <v>302.7406855511736</v>
       </c>
       <c r="B29" t="n">
-        <v>4033</v>
+        <v>16819</v>
       </c>
       <c r="C29" t="n">
-        <v>72.59399999999999</v>
+        <v>302.742</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008595449583651771</v>
+        <v>0.001314448826462922</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>72.74985905465556</v>
+        <v>315.1397529006813</v>
       </c>
       <c r="B30" t="n">
-        <v>4042</v>
+        <v>17508</v>
       </c>
       <c r="C30" t="n">
-        <v>72.756</v>
+        <v>315.144</v>
       </c>
       <c r="D30" t="n">
-        <v>0.006140945344441207</v>
+        <v>0.004247099318718028</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73.67071513726972</v>
+        <v>327.5388202501892</v>
       </c>
       <c r="B31" t="n">
-        <v>4093</v>
+        <v>18197</v>
       </c>
       <c r="C31" t="n">
-        <v>73.67399999999999</v>
+        <v>327.546</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003284862730268401</v>
+        <v>0.007179749810745761</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79.32759351859701</v>
+        <v>335.2018653009841</v>
       </c>
       <c r="B32" t="n">
-        <v>4407</v>
+        <v>18622</v>
       </c>
       <c r="C32" t="n">
-        <v>79.32599999999999</v>
+        <v>335.196</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001593518597019283</v>
+        <v>-0.005865300984112309</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80.41290410545039</v>
+        <v>347.600932650492</v>
       </c>
       <c r="B33" t="n">
-        <v>4467</v>
+        <v>19311</v>
       </c>
       <c r="C33" t="n">
-        <v>80.40599999999999</v>
+        <v>347.598</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006904105450402653</v>
+        <v>-0.002932650492027733</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>86.06978248677768</v>
+        <v>6.742188968180672</v>
       </c>
       <c r="B34" t="n">
-        <v>4782</v>
+        <v>375</v>
       </c>
       <c r="C34" t="n">
-        <v>86.07599999999999</v>
+        <v>6.75</v>
       </c>
       <c r="D34" t="n">
-        <v>0.006217513222310345</v>
+        <v>0.007811031819327852</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92.64751695071936</v>
+        <v>14.40523401897528</v>
       </c>
       <c r="B35" t="n">
-        <v>5147</v>
+        <v>800</v>
       </c>
       <c r="C35" t="n">
-        <v>92.646</v>
+        <v>14.4</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.001516950719363308</v>
+        <v>-0.005234018975279753</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>92.81197145495835</v>
+        <v>26.80430136848346</v>
       </c>
       <c r="B36" t="n">
-        <v>5156</v>
+        <v>1489</v>
       </c>
       <c r="C36" t="n">
-        <v>92.80799999999999</v>
+        <v>26.802</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.003971454958360709</v>
+        <v>-0.002301368483465183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99.38970591890003</v>
+        <v>34.46734641927807</v>
       </c>
       <c r="B37" t="n">
-        <v>5522</v>
+        <v>1915</v>
       </c>
       <c r="C37" t="n">
-        <v>99.396</v>
+        <v>34.47</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00629408109996632</v>
+        <v>0.002653580721926119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105.0465843002271</v>
+        <v>46.86641376878626</v>
       </c>
       <c r="B38" t="n">
-        <v>5836</v>
+        <v>2604</v>
       </c>
       <c r="C38" t="n">
-        <v>105.048</v>
+        <v>46.872</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001415699772906009</v>
+        <v>0.005586231213740689</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106.1318948870807</v>
+        <v>59.26548111829422</v>
       </c>
       <c r="B39" t="n">
-        <v>5896</v>
+        <v>3293</v>
       </c>
       <c r="C39" t="n">
-        <v>106.128</v>
+        <v>59.274</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.003894887080704734</v>
+        <v>0.008518881705782633</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111.7887732684078</v>
+        <v>66.92852616908905</v>
       </c>
       <c r="B40" t="n">
-        <v>6210</v>
+        <v>3718</v>
       </c>
       <c r="C40" t="n">
-        <v>111.78</v>
+        <v>66.92399999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.008773268407765045</v>
+        <v>-0.004526169089061227</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112.7096293510222</v>
+        <v>79.32759351859701</v>
       </c>
       <c r="B41" t="n">
-        <v>6262</v>
+        <v>4407</v>
       </c>
       <c r="C41" t="n">
-        <v>112.716</v>
+        <v>79.32599999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>0.006370648977835458</v>
+        <v>-0.001593518597019283</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112.8740838552614</v>
+        <v>99.38970591890003</v>
       </c>
       <c r="B42" t="n">
-        <v>6271</v>
+        <v>5522</v>
       </c>
       <c r="C42" t="n">
-        <v>112.878</v>
+        <v>99.396</v>
       </c>
       <c r="D42" t="n">
-        <v>0.003916144738624894</v>
+        <v>0.00629408109996632</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118.5309622365884</v>
+        <v>111.7887732684078</v>
       </c>
       <c r="B43" t="n">
-        <v>6585</v>
+        <v>6210</v>
       </c>
       <c r="C43" t="n">
-        <v>118.53</v>
+        <v>111.78</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0009622365884354167</v>
+        <v>-0.008773268407765045</v>
       </c>
     </row>
     <row r="44">
@@ -1045,590 +1045,590 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125.1086967005299</v>
+        <v>131.8508856687106</v>
       </c>
       <c r="B45" t="n">
-        <v>6950</v>
+        <v>7325</v>
       </c>
       <c r="C45" t="n">
-        <v>125.1</v>
+        <v>131.85</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.008696700529895907</v>
+        <v>-0.0008856687105662786</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125.2731512047691</v>
+        <v>144.2499530182185</v>
       </c>
       <c r="B46" t="n">
-        <v>6960</v>
+        <v>8014</v>
       </c>
       <c r="C46" t="n">
-        <v>125.28</v>
+        <v>144.252</v>
       </c>
       <c r="D46" t="n">
-        <v>0.006848795230894211</v>
+        <v>0.002046981781489876</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126.1940072873835</v>
+        <v>151.9129980690134</v>
       </c>
       <c r="B47" t="n">
-        <v>7011</v>
+        <v>8440</v>
       </c>
       <c r="C47" t="n">
-        <v>126.198</v>
+        <v>151.92</v>
       </c>
       <c r="D47" t="n">
-        <v>0.003992712616494032</v>
+        <v>0.007001930986632487</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131.8508856687106</v>
+        <v>164.3120654185213</v>
       </c>
       <c r="B48" t="n">
-        <v>7325</v>
+        <v>9128</v>
       </c>
       <c r="C48" t="n">
-        <v>131.85</v>
+        <v>164.304</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0008856687105662786</v>
+        <v>-0.00806541852131204</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132.9361962555642</v>
+        <v>171.9751104693166</v>
       </c>
       <c r="B49" t="n">
-        <v>7385</v>
+        <v>9554</v>
       </c>
       <c r="C49" t="n">
-        <v>132.93</v>
+        <v>171.972</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.006196255564162811</v>
+        <v>-0.003110469316595754</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137.5077640500378</v>
+        <v>184.3741778188239</v>
       </c>
       <c r="B50" t="n">
-        <v>7639</v>
+        <v>10243</v>
       </c>
       <c r="C50" t="n">
-        <v>137.502</v>
+        <v>184.374</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.005764050037839752</v>
+        <v>-0.0001778188238859002</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>138.5930746368912</v>
+        <v>196.7732451683321</v>
       </c>
       <c r="B51" t="n">
-        <v>7700</v>
+        <v>10932</v>
       </c>
       <c r="C51" t="n">
-        <v>138.6</v>
+        <v>196.776</v>
       </c>
       <c r="D51" t="n">
-        <v>0.006925363108763349</v>
+        <v>0.002754831667914459</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>144.2499530182185</v>
+        <v>204.4362902191267</v>
       </c>
       <c r="B52" t="n">
-        <v>8014</v>
+        <v>11358</v>
       </c>
       <c r="C52" t="n">
-        <v>144.252</v>
+        <v>204.444</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002046981781489876</v>
+        <v>0.007709780873312866</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>145.1708091008327</v>
+        <v>216.8353575686349</v>
       </c>
       <c r="B53" t="n">
-        <v>8065</v>
+        <v>12046</v>
       </c>
       <c r="C53" t="n">
-        <v>145.17</v>
+        <v>216.828</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0008091008326971405</v>
+        <v>-0.007357568634859035</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>145.3352636050719</v>
+        <v>236.8974699689377</v>
       </c>
       <c r="B54" t="n">
-        <v>8074</v>
+        <v>13161</v>
       </c>
       <c r="C54" t="n">
-        <v>145.332</v>
+        <v>236.898</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.003263605071907705</v>
+        <v>0.0005300310623397309</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>150.9921419863992</v>
+        <v>249.2965373184456</v>
       </c>
       <c r="B55" t="n">
-        <v>8388</v>
+        <v>13850</v>
       </c>
       <c r="C55" t="n">
-        <v>150.984</v>
+        <v>249.3</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.008141986399181178</v>
+        <v>0.003462681554367464</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>151.9129980690134</v>
+        <v>256.9595823692405</v>
       </c>
       <c r="B56" t="n">
-        <v>8440</v>
+        <v>14276</v>
       </c>
       <c r="C56" t="n">
-        <v>151.92</v>
+        <v>256.968</v>
       </c>
       <c r="D56" t="n">
-        <v>0.007001930986632487</v>
+        <v>0.008417630759538497</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>157.5698764503406</v>
+        <v>269.3586497187487</v>
       </c>
       <c r="B57" t="n">
-        <v>8754</v>
+        <v>14964</v>
       </c>
       <c r="C57" t="n">
-        <v>157.572</v>
+        <v>269.352</v>
       </c>
       <c r="D57" t="n">
-        <v>0.002123549659359014</v>
+        <v>-0.006649718748690248</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>157.7343309545799</v>
+        <v>281.7577170682564</v>
       </c>
       <c r="B58" t="n">
-        <v>8763</v>
+        <v>15653</v>
       </c>
       <c r="C58" t="n">
-        <v>157.734</v>
+        <v>281.754</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0003309545798515501</v>
+        <v>-0.003717068256378298</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>158.655187037194</v>
+        <v>289.4207621190515</v>
       </c>
       <c r="B59" t="n">
-        <v>8814</v>
+        <v>16079</v>
       </c>
       <c r="C59" t="n">
-        <v>158.652</v>
+        <v>289.422</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.003187037194038567</v>
+        <v>0.001237880948508518</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>164.3120654185213</v>
+        <v>301.8198294685592</v>
       </c>
       <c r="B60" t="n">
-        <v>9128</v>
+        <v>16768</v>
       </c>
       <c r="C60" t="n">
-        <v>164.304</v>
+        <v>301.824</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.00806541852131204</v>
+        <v>0.004170531440820469</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>165.2329215011359</v>
+        <v>309.4828745193543</v>
       </c>
       <c r="B61" t="n">
-        <v>9180</v>
+        <v>17193</v>
       </c>
       <c r="C61" t="n">
-        <v>165.24</v>
+        <v>309.474</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0070784988640753</v>
+        <v>-0.008874519354264976</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>165.3973760053747</v>
+        <v>321.881941868862</v>
       </c>
       <c r="B62" t="n">
-        <v>9189</v>
+        <v>17882</v>
       </c>
       <c r="C62" t="n">
-        <v>165.402</v>
+        <v>321.876</v>
       </c>
       <c r="D62" t="n">
-        <v>0.004623994625291061</v>
+        <v>-0.005941868862009869</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>171.054254386702</v>
+        <v>334.2810092183699</v>
       </c>
       <c r="B63" t="n">
-        <v>9503</v>
+        <v>18571</v>
       </c>
       <c r="C63" t="n">
-        <v>171.054</v>
+        <v>334.278</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.000254386701982412</v>
+        <v>-0.003009218369982136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>171.9751104693166</v>
+        <v>341.9440542691648</v>
       </c>
       <c r="B64" t="n">
-        <v>9554</v>
+        <v>18997</v>
       </c>
       <c r="C64" t="n">
-        <v>171.972</v>
+        <v>341.946</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.003110469316595754</v>
+        <v>0.001945730835188897</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>177.6319888506432</v>
+        <v>354.3431216186727</v>
       </c>
       <c r="B65" t="n">
-        <v>9868</v>
+        <v>19686</v>
       </c>
       <c r="C65" t="n">
-        <v>177.624</v>
+        <v>354.348</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.007988850643215528</v>
+        <v>0.004878381327273473</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>177.7964433548827</v>
+        <v>1.085310586853382</v>
       </c>
       <c r="B66" t="n">
-        <v>9878</v>
+        <v>60</v>
       </c>
       <c r="C66" t="n">
-        <v>177.804</v>
+        <v>1.08</v>
       </c>
       <c r="D66" t="n">
-        <v>0.007556645117347216</v>
+        <v>-0.005310586853381594</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>178.7172994374973</v>
+        <v>13.48437793636134</v>
       </c>
       <c r="B67" t="n">
-        <v>9929</v>
+        <v>749</v>
       </c>
       <c r="C67" t="n">
-        <v>178.722</v>
+        <v>13.482</v>
       </c>
       <c r="D67" t="n">
-        <v>0.004700562502733874</v>
+        <v>-0.002377936361344979</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>184.3741778188239</v>
+        <v>21.14742298715595</v>
       </c>
       <c r="B68" t="n">
-        <v>10243</v>
+        <v>1175</v>
       </c>
       <c r="C68" t="n">
-        <v>184.374</v>
+        <v>21.15</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.0001778188238859002</v>
+        <v>0.002577012844046322</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>185.4594884056779</v>
+        <v>33.54649033666414</v>
       </c>
       <c r="B69" t="n">
-        <v>10303</v>
+        <v>1864</v>
       </c>
       <c r="C69" t="n">
-        <v>185.454</v>
+        <v>33.552</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.00548840567793718</v>
+        <v>0.005509663335864445</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>190.0310562001514</v>
+        <v>41.20953538745874</v>
       </c>
       <c r="B70" t="n">
-        <v>10557</v>
+        <v>2289</v>
       </c>
       <c r="C70" t="n">
-        <v>190.026</v>
+        <v>41.202</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.005056200151415169</v>
+        <v>-0.007535387458744935</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>191.1163667870046</v>
+        <v>53.60860273696693</v>
       </c>
       <c r="B71" t="n">
-        <v>10618</v>
+        <v>2978</v>
       </c>
       <c r="C71" t="n">
-        <v>191.124</v>
+        <v>53.604</v>
       </c>
       <c r="D71" t="n">
-        <v>0.007633212995443728</v>
+        <v>-0.004602736966930365</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>196.7732451683321</v>
+        <v>66.00767008647489</v>
       </c>
       <c r="B72" t="n">
-        <v>10932</v>
+        <v>3667</v>
       </c>
       <c r="C72" t="n">
-        <v>196.776</v>
+        <v>66.006</v>
       </c>
       <c r="D72" t="n">
-        <v>0.002754831667914459</v>
+        <v>-0.001670086474888421</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>197.694101250946</v>
+        <v>73.67071513726972</v>
       </c>
       <c r="B73" t="n">
-        <v>10983</v>
+        <v>4093</v>
       </c>
       <c r="C73" t="n">
-        <v>197.694</v>
+        <v>73.67399999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0001012509460167621</v>
+        <v>0.003284862730268401</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>197.8585557551852</v>
+        <v>86.06978248677768</v>
       </c>
       <c r="B74" t="n">
-        <v>10992</v>
+        <v>4782</v>
       </c>
       <c r="C74" t="n">
-        <v>197.856</v>
+        <v>86.07599999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.002555755185227326</v>
+        <v>0.006217513222310345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>203.5154341365127</v>
+        <v>106.1318948870807</v>
       </c>
       <c r="B75" t="n">
-        <v>11306</v>
+        <v>5896</v>
       </c>
       <c r="C75" t="n">
-        <v>203.508</v>
+        <v>106.128</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.007434136512756595</v>
+        <v>-0.003894887080704734</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>204.4362902191267</v>
+        <v>118.5309622365884</v>
       </c>
       <c r="B76" t="n">
-        <v>11358</v>
+        <v>6585</v>
       </c>
       <c r="C76" t="n">
-        <v>204.444</v>
+        <v>118.53</v>
       </c>
       <c r="D76" t="n">
-        <v>0.007709780873312866</v>
+        <v>-0.0009622365884354167</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>210.0931686004542</v>
+        <v>126.1940072873835</v>
       </c>
       <c r="B77" t="n">
-        <v>11672</v>
+        <v>7011</v>
       </c>
       <c r="C77" t="n">
-        <v>210.096</v>
+        <v>126.198</v>
       </c>
       <c r="D77" t="n">
-        <v>0.002831399545812019</v>
+        <v>0.003992712616494032</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>210.2576231046934</v>
+        <v>138.5930746368912</v>
       </c>
       <c r="B78" t="n">
-        <v>11681</v>
+        <v>7700</v>
       </c>
       <c r="C78" t="n">
-        <v>210.258</v>
+        <v>138.6</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0003768953065730329</v>
+        <v>0.006925363108763349</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>211.1784791873073</v>
+        <v>150.9921419863992</v>
       </c>
       <c r="B79" t="n">
-        <v>11732</v>
+        <v>8388</v>
       </c>
       <c r="C79" t="n">
-        <v>211.176</v>
+        <v>150.984</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.002479187307358188</v>
+        <v>-0.008141986399181178</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>216.8353575686349</v>
+        <v>158.655187037194</v>
       </c>
       <c r="B80" t="n">
-        <v>12046</v>
+        <v>8814</v>
       </c>
       <c r="C80" t="n">
-        <v>216.828</v>
+        <v>158.652</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.007357568634859035</v>
+        <v>-0.003187037194038567</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>217.920668155488</v>
+        <v>171.054254386702</v>
       </c>
       <c r="B81" t="n">
-        <v>12107</v>
+        <v>9503</v>
       </c>
       <c r="C81" t="n">
-        <v>217.926</v>
+        <v>171.054</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00533184451197144</v>
+        <v>-0.000254386701982412</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>223.5775465368155</v>
+        <v>178.7172994374973</v>
       </c>
       <c r="B82" t="n">
-        <v>12421</v>
+        <v>9929</v>
       </c>
       <c r="C82" t="n">
-        <v>223.578</v>
+        <v>178.722</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0004534631844705928</v>
+        <v>0.004700562502733874</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>230.155281000757</v>
+        <v>191.1163667870046</v>
       </c>
       <c r="B83" t="n">
-        <v>12786</v>
+        <v>10618</v>
       </c>
       <c r="C83" t="n">
-        <v>230.148</v>
+        <v>191.124</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.007281000756989897</v>
+        <v>0.007633212995443728</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>230.3197355049962</v>
+        <v>203.5154341365127</v>
       </c>
       <c r="B84" t="n">
-        <v>12796</v>
+        <v>11306</v>
       </c>
       <c r="C84" t="n">
-        <v>230.328</v>
+        <v>203.508</v>
       </c>
       <c r="D84" t="n">
-        <v>0.008264495003800221</v>
+        <v>-0.007434136512756595</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>236.8974699689377</v>
+        <v>211.1784791873073</v>
       </c>
       <c r="B85" t="n">
-        <v>13161</v>
+        <v>11732</v>
       </c>
       <c r="C85" t="n">
-        <v>236.898</v>
+        <v>211.176</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0005300310623397309</v>
+        <v>-0.002479187307358188</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>242.5543483502649</v>
+        <v>223.5775465368155</v>
       </c>
       <c r="B86" t="n">
-        <v>13475</v>
+        <v>12421</v>
       </c>
       <c r="C86" t="n">
-        <v>242.55</v>
+        <v>223.578</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.004348350264962164</v>
+        <v>0.0004534631844705928</v>
       </c>
     </row>
     <row r="87">
@@ -1647,576 +1647,576 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>249.2965373184456</v>
+        <v>256.0387262866263</v>
       </c>
       <c r="B88" t="n">
-        <v>13850</v>
+        <v>14224</v>
       </c>
       <c r="C88" t="n">
-        <v>249.3</v>
+        <v>256.032</v>
       </c>
       <c r="D88" t="n">
-        <v>0.003462681554367464</v>
+        <v>-0.00672628662630359</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>250.2173934010598</v>
+        <v>263.7017713374211</v>
       </c>
       <c r="B89" t="n">
-        <v>13901</v>
+        <v>14650</v>
       </c>
       <c r="C89" t="n">
-        <v>250.218</v>
+        <v>263.7</v>
       </c>
       <c r="D89" t="n">
-        <v>0.000606598940208869</v>
+        <v>-0.001771337421132557</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>250.381847905299</v>
+        <v>276.1008386869293</v>
       </c>
       <c r="B90" t="n">
-        <v>13910</v>
+        <v>15339</v>
       </c>
       <c r="C90" t="n">
-        <v>250.38</v>
+        <v>276.102</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.001847905299001695</v>
+        <v>0.001161313070667802</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>256.0387262866263</v>
+        <v>288.499906036437</v>
       </c>
       <c r="B91" t="n">
-        <v>14224</v>
+        <v>16028</v>
       </c>
       <c r="C91" t="n">
-        <v>256.032</v>
+        <v>288.504</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.00672628662630359</v>
+        <v>0.004093963562979752</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>256.9595823692405</v>
+        <v>296.1629510872321</v>
       </c>
       <c r="B92" t="n">
-        <v>14276</v>
+        <v>16453</v>
       </c>
       <c r="C92" t="n">
-        <v>256.968</v>
+        <v>296.154</v>
       </c>
       <c r="D92" t="n">
-        <v>0.008417630759538497</v>
+        <v>-0.008951087232105692</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>262.616460750568</v>
+        <v>308.5620184367398</v>
       </c>
       <c r="B93" t="n">
-        <v>14590</v>
+        <v>17142</v>
       </c>
       <c r="C93" t="n">
-        <v>262.62</v>
+        <v>308.556</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00353924943203765</v>
+        <v>-0.006018436739850586</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>262.780915254807</v>
+        <v>316.2250634875349</v>
       </c>
       <c r="B94" t="n">
-        <v>14599</v>
+        <v>17568</v>
       </c>
       <c r="C94" t="n">
-        <v>262.782</v>
+        <v>316.224</v>
       </c>
       <c r="D94" t="n">
-        <v>0.001084745192997616</v>
+        <v>-0.001063487534906926</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>263.7017713374211</v>
+        <v>328.6241308370426</v>
       </c>
       <c r="B95" t="n">
-        <v>14650</v>
+        <v>18257</v>
       </c>
       <c r="C95" t="n">
-        <v>263.7</v>
+        <v>328.626</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.001771337421132557</v>
+        <v>0.00186916295734818</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>269.3586497187487</v>
+        <v>341.0231981865506</v>
       </c>
       <c r="B96" t="n">
-        <v>14964</v>
+        <v>18946</v>
       </c>
       <c r="C96" t="n">
-        <v>269.352</v>
+        <v>341.028</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.006649718748690248</v>
+        <v>0.004801813449375913</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>270.4439603056018</v>
+        <v>348.6862432373454</v>
       </c>
       <c r="B97" t="n">
-        <v>15025</v>
+        <v>19371</v>
       </c>
       <c r="C97" t="n">
-        <v>270.45</v>
+        <v>348.678</v>
       </c>
       <c r="D97" t="n">
-        <v>0.006039694398168649</v>
+        <v>-0.008243237345425314</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>275.0155281000757</v>
+        <v>7.82749955503408</v>
       </c>
       <c r="B98" t="n">
-        <v>15279</v>
+        <v>435</v>
       </c>
       <c r="C98" t="n">
-        <v>275.022</v>
+        <v>7.83</v>
       </c>
       <c r="D98" t="n">
-        <v>0.006471899924292757</v>
+        <v>0.002500444965919613</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>276.1008386869293</v>
+        <v>20.22656690454201</v>
       </c>
       <c r="B99" t="n">
-        <v>15339</v>
+        <v>1124</v>
       </c>
       <c r="C99" t="n">
-        <v>276.102</v>
+        <v>20.232</v>
       </c>
       <c r="D99" t="n">
-        <v>0.001161313070667802</v>
+        <v>0.005433095457984649</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>281.7577170682564</v>
+        <v>27.88961195533662</v>
       </c>
       <c r="B100" t="n">
-        <v>15653</v>
+        <v>1549</v>
       </c>
       <c r="C100" t="n">
-        <v>281.754</v>
+        <v>27.882</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.003717068256378298</v>
+        <v>-0.007611955336624732</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>282.6785731508708</v>
+        <v>40.28867930484481</v>
       </c>
       <c r="B101" t="n">
-        <v>15704</v>
+        <v>2238</v>
       </c>
       <c r="C101" t="n">
-        <v>282.672</v>
+        <v>40.284</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.006573150870792688</v>
+        <v>-0.004679304844806609</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>282.84302765511</v>
+        <v>47.95172435563941</v>
       </c>
       <c r="B102" t="n">
-        <v>15714</v>
+        <v>2664</v>
       </c>
       <c r="C102" t="n">
-        <v>282.852</v>
+        <v>47.952</v>
       </c>
       <c r="D102" t="n">
-        <v>0.008972344889969008</v>
+        <v>0.0002756443605846925</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>288.499906036437</v>
+        <v>60.3507917051476</v>
       </c>
       <c r="B103" t="n">
-        <v>16028</v>
+        <v>3353</v>
       </c>
       <c r="C103" t="n">
-        <v>288.504</v>
+        <v>60.354</v>
       </c>
       <c r="D103" t="n">
-        <v>0.004093963562979752</v>
+        <v>0.003208294852399263</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>289.4207621190515</v>
+        <v>72.74985905465556</v>
       </c>
       <c r="B104" t="n">
-        <v>16079</v>
+        <v>4042</v>
       </c>
       <c r="C104" t="n">
-        <v>289.422</v>
+        <v>72.756</v>
       </c>
       <c r="D104" t="n">
-        <v>0.001237880948508518</v>
+        <v>0.006140945344441207</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>295.0776405003785</v>
+        <v>80.41290410545039</v>
       </c>
       <c r="B105" t="n">
-        <v>16393</v>
+        <v>4467</v>
       </c>
       <c r="C105" t="n">
-        <v>295.074</v>
+        <v>80.40599999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.003640500378480738</v>
+        <v>-0.006904105450402653</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>295.2420950046177</v>
+        <v>92.81197145495835</v>
       </c>
       <c r="B106" t="n">
-        <v>16402</v>
+        <v>5156</v>
       </c>
       <c r="C106" t="n">
-        <v>295.236</v>
+        <v>92.80799999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.006095004617748145</v>
+        <v>-0.003971454958360709</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>296.1629510872321</v>
+        <v>112.8740838552614</v>
       </c>
       <c r="B107" t="n">
-        <v>16453</v>
+        <v>6271</v>
       </c>
       <c r="C107" t="n">
-        <v>296.154</v>
+        <v>112.878</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.008951087232105692</v>
+        <v>0.003916144738624894</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>301.8198294685592</v>
+        <v>125.2731512047691</v>
       </c>
       <c r="B108" t="n">
-        <v>16768</v>
+        <v>6960</v>
       </c>
       <c r="C108" t="n">
-        <v>301.824</v>
+        <v>125.28</v>
       </c>
       <c r="D108" t="n">
-        <v>0.004170531440820469</v>
+        <v>0.006848795230894211</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>302.7406855511736</v>
+        <v>132.9361962555642</v>
       </c>
       <c r="B109" t="n">
-        <v>16819</v>
+        <v>7385</v>
       </c>
       <c r="C109" t="n">
-        <v>302.742</v>
+        <v>132.93</v>
       </c>
       <c r="D109" t="n">
-        <v>0.001314448826462922</v>
+        <v>-0.006196255564162811</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>302.9051400554128</v>
+        <v>145.3352636050719</v>
       </c>
       <c r="B110" t="n">
-        <v>16828</v>
+        <v>8074</v>
       </c>
       <c r="C110" t="n">
-        <v>302.904</v>
+        <v>145.332</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.001140055412804486</v>
+        <v>-0.003263605071907705</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>308.5620184367398</v>
+        <v>157.7343309545799</v>
       </c>
       <c r="B111" t="n">
-        <v>17142</v>
+        <v>8763</v>
       </c>
       <c r="C111" t="n">
-        <v>308.556</v>
+        <v>157.734</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.006018436739850586</v>
+        <v>-0.0003309545798515501</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>309.4828745193543</v>
+        <v>165.3973760053747</v>
       </c>
       <c r="B112" t="n">
-        <v>17193</v>
+        <v>9189</v>
       </c>
       <c r="C112" t="n">
-        <v>309.474</v>
+        <v>165.402</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.008874519354264976</v>
+        <v>0.004623994625291061</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>315.1397529006813</v>
+        <v>177.7964433548827</v>
       </c>
       <c r="B113" t="n">
-        <v>17508</v>
+        <v>9878</v>
       </c>
       <c r="C113" t="n">
-        <v>315.144</v>
+        <v>177.804</v>
       </c>
       <c r="D113" t="n">
-        <v>0.004247099318718028</v>
+        <v>0.007556645117347216</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>315.3042074049205</v>
+        <v>185.4594884056779</v>
       </c>
       <c r="B114" t="n">
-        <v>17517</v>
+        <v>10303</v>
       </c>
       <c r="C114" t="n">
-        <v>315.306</v>
+        <v>185.454</v>
       </c>
       <c r="D114" t="n">
-        <v>0.001792595079450621</v>
+        <v>-0.00548840567793718</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>316.2250634875349</v>
+        <v>197.8585557551852</v>
       </c>
       <c r="B115" t="n">
-        <v>17568</v>
+        <v>10992</v>
       </c>
       <c r="C115" t="n">
-        <v>316.224</v>
+        <v>197.856</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.001063487534906926</v>
+        <v>-0.002555755185227326</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>321.881941868862</v>
+        <v>210.2576231046934</v>
       </c>
       <c r="B116" t="n">
-        <v>17882</v>
+        <v>11681</v>
       </c>
       <c r="C116" t="n">
-        <v>321.876</v>
+        <v>210.258</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.005941868862009869</v>
+        <v>0.0003768953065730329</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>322.9672524557156</v>
+        <v>217.920668155488</v>
       </c>
       <c r="B117" t="n">
-        <v>17943</v>
+        <v>12107</v>
       </c>
       <c r="C117" t="n">
-        <v>322.974</v>
+        <v>217.926</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00674754428439428</v>
+        <v>0.00533184451197144</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>327.5388202501892</v>
+        <v>230.3197355049962</v>
       </c>
       <c r="B118" t="n">
-        <v>18197</v>
+        <v>12796</v>
       </c>
       <c r="C118" t="n">
-        <v>327.546</v>
+        <v>230.328</v>
       </c>
       <c r="D118" t="n">
-        <v>0.007179749810745761</v>
+        <v>0.008264495003800221</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>328.6241308370426</v>
+        <v>250.381847905299</v>
       </c>
       <c r="B119" t="n">
-        <v>18257</v>
+        <v>13910</v>
       </c>
       <c r="C119" t="n">
-        <v>328.626</v>
+        <v>250.38</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00186916295734818</v>
+        <v>-0.001847905299001695</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>334.2810092183699</v>
+        <v>262.780915254807</v>
       </c>
       <c r="B120" t="n">
-        <v>18571</v>
+        <v>14599</v>
       </c>
       <c r="C120" t="n">
-        <v>334.278</v>
+        <v>262.782</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.003009218369982136</v>
+        <v>0.001084745192997616</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>335.2018653009841</v>
+        <v>270.4439603056018</v>
       </c>
       <c r="B121" t="n">
-        <v>18622</v>
+        <v>15025</v>
       </c>
       <c r="C121" t="n">
-        <v>335.196</v>
+        <v>270.45</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.005865300984112309</v>
+        <v>0.006039694398168649</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>335.3663198052233</v>
+        <v>282.84302765511</v>
       </c>
       <c r="B122" t="n">
-        <v>18631</v>
+        <v>15714</v>
       </c>
       <c r="C122" t="n">
-        <v>335.358</v>
+        <v>282.852</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.008319805223322874</v>
+        <v>0.008972344889969008</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>341.0231981865506</v>
+        <v>295.2420950046177</v>
       </c>
       <c r="B123" t="n">
-        <v>18946</v>
+        <v>16402</v>
       </c>
       <c r="C123" t="n">
-        <v>341.028</v>
+        <v>295.236</v>
       </c>
       <c r="D123" t="n">
-        <v>0.004801813449375913</v>
+        <v>-0.006095004617748145</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>341.9440542691648</v>
+        <v>302.9051400554128</v>
       </c>
       <c r="B124" t="n">
-        <v>18997</v>
+        <v>16828</v>
       </c>
       <c r="C124" t="n">
-        <v>341.946</v>
+        <v>302.904</v>
       </c>
       <c r="D124" t="n">
-        <v>0.001945730835188897</v>
+        <v>-0.001140055412804486</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>347.600932650492</v>
+        <v>315.3042074049205</v>
       </c>
       <c r="B125" t="n">
-        <v>19311</v>
+        <v>17517</v>
       </c>
       <c r="C125" t="n">
-        <v>347.598</v>
+        <v>315.306</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.002932650492027733</v>
+        <v>0.001792595079450621</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>347.7653871547313</v>
+        <v>322.9672524557156</v>
       </c>
       <c r="B126" t="n">
-        <v>19320</v>
+        <v>17943</v>
       </c>
       <c r="C126" t="n">
-        <v>347.76</v>
+        <v>322.974</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.005387154731295141</v>
+        <v>0.00674754428439428</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>348.6862432373454</v>
+        <v>335.3663198052233</v>
       </c>
       <c r="B127" t="n">
-        <v>19371</v>
+        <v>18631</v>
       </c>
       <c r="C127" t="n">
-        <v>348.678</v>
+        <v>335.358</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.008243237345425314</v>
+        <v>-0.008319805223322874</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>354.3431216186727</v>
+        <v>347.7653871547313</v>
       </c>
       <c r="B128" t="n">
-        <v>19686</v>
+        <v>19320</v>
       </c>
       <c r="C128" t="n">
-        <v>354.348</v>
+        <v>347.76</v>
       </c>
       <c r="D128" t="n">
-        <v>0.004878381327273473</v>
+        <v>-0.005387154731295141</v>
       </c>
     </row>
     <row r="129">
@@ -2250,7 +2250,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_unwrapped_acq</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2285,1780 +2285,1780 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794609</v>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08</v>
+        <v>7.668</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.005310586853381594</v>
+        <v>0.004954949205391301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.742188968180673</v>
+        <v>20.06211240030279</v>
       </c>
       <c r="B4" t="n">
-        <v>375</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>6.75</v>
+        <v>20.07</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007811031819326963</v>
+        <v>0.007887599697205872</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.663045050794609</v>
+        <v>27.7251574510974</v>
       </c>
       <c r="B5" t="n">
-        <v>426</v>
+        <v>1540</v>
       </c>
       <c r="C5" t="n">
-        <v>7.668</v>
+        <v>27.72</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004954949205391301</v>
+        <v>-0.005157451097403509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.82749955503408</v>
+        <v>40.12422480060559</v>
       </c>
       <c r="B6" t="n">
-        <v>435</v>
+        <v>2229</v>
       </c>
       <c r="C6" t="n">
-        <v>7.83</v>
+        <v>40.122</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002500444965919613</v>
+        <v>-0.002224800605588939</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.48437793636135</v>
+        <v>52.52329215011355</v>
       </c>
       <c r="B7" t="n">
-        <v>749</v>
+        <v>2918</v>
       </c>
       <c r="C7" t="n">
-        <v>13.482</v>
+        <v>52.524</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002377936361346755</v>
+        <v>0.0007078498864530047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14.40523401897528</v>
+        <v>60.18633720090838</v>
       </c>
       <c r="B8" t="n">
-        <v>800</v>
+        <v>3344</v>
       </c>
       <c r="C8" t="n">
-        <v>14.4</v>
+        <v>60.192</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.005234018975277976</v>
+        <v>0.005662799091624038</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20.06211240030279</v>
+        <v>72.58540455041634</v>
       </c>
       <c r="B9" t="n">
-        <v>1115</v>
+        <v>4033</v>
       </c>
       <c r="C9" t="n">
-        <v>20.07</v>
+        <v>72.59399999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007887599697205872</v>
+        <v>0.008595449583651771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20.22656690454201</v>
+        <v>92.64751695071936</v>
       </c>
       <c r="B10" t="n">
-        <v>1124</v>
+        <v>5147</v>
       </c>
       <c r="C10" t="n">
-        <v>20.232</v>
+        <v>92.646</v>
       </c>
       <c r="D10" t="n">
-        <v>0.005433095457984649</v>
+        <v>-0.001516950719363308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21.14742298715595</v>
+        <v>105.0465843002271</v>
       </c>
       <c r="B11" t="n">
-        <v>1175</v>
+        <v>5836</v>
       </c>
       <c r="C11" t="n">
-        <v>21.15</v>
+        <v>105.048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002577012844046322</v>
+        <v>0.001415699772906009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26.80430136848346</v>
+        <v>112.7096293510222</v>
       </c>
       <c r="B12" t="n">
-        <v>1489</v>
+        <v>6262</v>
       </c>
       <c r="C12" t="n">
-        <v>26.802</v>
+        <v>112.716</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.002301368483465183</v>
+        <v>0.006370648977835458</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27.7251574510974</v>
+        <v>125.1086967005299</v>
       </c>
       <c r="B13" t="n">
-        <v>1540</v>
+        <v>6950</v>
       </c>
       <c r="C13" t="n">
-        <v>27.72</v>
+        <v>125.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.005157451097403509</v>
+        <v>-0.008696700529910117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27.88961195533662</v>
+        <v>137.5077640500378</v>
       </c>
       <c r="B14" t="n">
-        <v>1549</v>
+        <v>7639</v>
       </c>
       <c r="C14" t="n">
-        <v>27.882</v>
+        <v>137.502</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.007611955336624732</v>
+        <v>-0.005764050037839752</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33.54649033666414</v>
+        <v>145.1708091008327</v>
       </c>
       <c r="B15" t="n">
-        <v>1864</v>
+        <v>8065</v>
       </c>
       <c r="C15" t="n">
-        <v>33.552</v>
+        <v>145.17</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005509663335864445</v>
+        <v>-0.0008091008326971405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>34.46734641927807</v>
+        <v>157.5698764503406</v>
       </c>
       <c r="B16" t="n">
-        <v>1915</v>
+        <v>8754</v>
       </c>
       <c r="C16" t="n">
-        <v>34.47</v>
+        <v>157.572</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002653580721926119</v>
+        <v>0.002123549659359014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40.12422480060559</v>
+        <v>165.2329215011359</v>
       </c>
       <c r="B17" t="n">
-        <v>2229</v>
+        <v>9180</v>
       </c>
       <c r="C17" t="n">
-        <v>40.122</v>
+        <v>165.24</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002224800605588939</v>
+        <v>0.0070784988640753</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40.28867930484481</v>
+        <v>177.6319888506432</v>
       </c>
       <c r="B18" t="n">
-        <v>2238</v>
+        <v>9868</v>
       </c>
       <c r="C18" t="n">
-        <v>40.284</v>
+        <v>177.624</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004679304844806609</v>
+        <v>-0.007988850643215528</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41.20953538745874</v>
+        <v>190.0310562001514</v>
       </c>
       <c r="B19" t="n">
-        <v>2289</v>
+        <v>10557</v>
       </c>
       <c r="C19" t="n">
-        <v>41.202</v>
+        <v>190.026</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.007535387458744935</v>
+        <v>-0.005056200151415169</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.86641376878626</v>
+        <v>197.694101250946</v>
       </c>
       <c r="B20" t="n">
-        <v>2604</v>
+        <v>10983</v>
       </c>
       <c r="C20" t="n">
-        <v>46.872</v>
+        <v>197.694</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005586231213740689</v>
+        <v>-0.0001012509460167621</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47.95172435563941</v>
+        <v>210.0931686004542</v>
       </c>
       <c r="B21" t="n">
-        <v>2664</v>
+        <v>11672</v>
       </c>
       <c r="C21" t="n">
-        <v>47.952</v>
+        <v>210.096</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002756443605846925</v>
+        <v>0.002831399545812019</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52.52329215011355</v>
+        <v>230.155281000757</v>
       </c>
       <c r="B22" t="n">
-        <v>2918</v>
+        <v>12786</v>
       </c>
       <c r="C22" t="n">
-        <v>52.524</v>
+        <v>230.148</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0007078498864530047</v>
+        <v>-0.007281000756989897</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53.60860273696693</v>
+        <v>242.5543483502649</v>
       </c>
       <c r="B23" t="n">
-        <v>2978</v>
+        <v>13475</v>
       </c>
       <c r="C23" t="n">
-        <v>53.604</v>
+        <v>242.55</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.004602736966930365</v>
+        <v>-0.004348350264962164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59.26548111829421</v>
+        <v>250.2173934010598</v>
       </c>
       <c r="B24" t="n">
-        <v>3293</v>
+        <v>13901</v>
       </c>
       <c r="C24" t="n">
-        <v>59.274</v>
+        <v>250.218</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008518881705789738</v>
+        <v>0.0006065989401804472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60.18633720090838</v>
+        <v>262.616460750568</v>
       </c>
       <c r="B25" t="n">
-        <v>3344</v>
+        <v>14590</v>
       </c>
       <c r="C25" t="n">
-        <v>60.192</v>
+        <v>262.62</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005662799091624038</v>
+        <v>0.00353924943203765</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60.35079170514759</v>
+        <v>275.0155281000757</v>
       </c>
       <c r="B26" t="n">
-        <v>3353</v>
+        <v>15279</v>
       </c>
       <c r="C26" t="n">
-        <v>60.354</v>
+        <v>275.022</v>
       </c>
       <c r="D26" t="n">
-        <v>0.003208294852406368</v>
+        <v>0.006471899924292757</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66.00767008647489</v>
+        <v>282.6785731508708</v>
       </c>
       <c r="B27" t="n">
-        <v>3667</v>
+        <v>15704</v>
       </c>
       <c r="C27" t="n">
-        <v>66.006</v>
+        <v>282.672</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.001670086474888421</v>
+        <v>-0.006573150870792688</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66.92852616908905</v>
+        <v>295.0776405003785</v>
       </c>
       <c r="B28" t="n">
-        <v>3718</v>
+        <v>16393</v>
       </c>
       <c r="C28" t="n">
-        <v>66.92399999999999</v>
+        <v>295.074</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.004526169089061227</v>
+        <v>-0.003640500378480738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72.58540455041634</v>
+        <v>302.7406855511736</v>
       </c>
       <c r="B29" t="n">
-        <v>4033</v>
+        <v>16819</v>
       </c>
       <c r="C29" t="n">
-        <v>72.59399999999999</v>
+        <v>302.742</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008595449583651771</v>
+        <v>0.001314448826462922</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>72.74985905465556</v>
+        <v>315.1397529006813</v>
       </c>
       <c r="B30" t="n">
-        <v>4042</v>
+        <v>17508</v>
       </c>
       <c r="C30" t="n">
-        <v>72.756</v>
+        <v>315.144</v>
       </c>
       <c r="D30" t="n">
-        <v>0.006140945344441207</v>
+        <v>0.004247099318718028</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73.67071513726972</v>
+        <v>327.5388202501892</v>
       </c>
       <c r="B31" t="n">
-        <v>4093</v>
+        <v>18197</v>
       </c>
       <c r="C31" t="n">
-        <v>73.67399999999999</v>
+        <v>327.546</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003284862730268401</v>
+        <v>0.007179749810745761</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79.32759351859701</v>
+        <v>335.2018653009841</v>
       </c>
       <c r="B32" t="n">
-        <v>4407</v>
+        <v>18622</v>
       </c>
       <c r="C32" t="n">
-        <v>79.32599999999999</v>
+        <v>335.196</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001593518597019283</v>
+        <v>-0.005865300984112309</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80.41290410545039</v>
+        <v>347.600932650492</v>
       </c>
       <c r="B33" t="n">
-        <v>4467</v>
+        <v>19311</v>
       </c>
       <c r="C33" t="n">
-        <v>80.40599999999999</v>
+        <v>347.598</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006904105450402653</v>
+        <v>-0.002932650492027733</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>86.06978248677768</v>
+        <v>366.7421889681807</v>
       </c>
       <c r="B34" t="n">
-        <v>4782</v>
+        <v>20375</v>
       </c>
       <c r="C34" t="n">
-        <v>86.07599999999999</v>
+        <v>366.75</v>
       </c>
       <c r="D34" t="n">
-        <v>0.006217513222310345</v>
+        <v>0.007811031819301206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92.64751695071936</v>
+        <v>374.4052340189753</v>
       </c>
       <c r="B35" t="n">
-        <v>5147</v>
+        <v>20800</v>
       </c>
       <c r="C35" t="n">
-        <v>92.646</v>
+        <v>374.4</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.001516950719363308</v>
+        <v>-0.005234018975329491</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>92.81197145495835</v>
+        <v>386.8043013684834</v>
       </c>
       <c r="B36" t="n">
-        <v>5156</v>
+        <v>21489</v>
       </c>
       <c r="C36" t="n">
-        <v>92.80799999999999</v>
+        <v>386.802</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.003971454958360709</v>
+        <v>-0.002301368483472288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99.38970591890003</v>
+        <v>394.467346419278</v>
       </c>
       <c r="B37" t="n">
-        <v>5522</v>
+        <v>21915</v>
       </c>
       <c r="C37" t="n">
-        <v>99.396</v>
+        <v>394.47</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00629408109996632</v>
+        <v>0.002653580721926119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105.0465843002271</v>
+        <v>406.8664137687862</v>
       </c>
       <c r="B38" t="n">
-        <v>5836</v>
+        <v>22604</v>
       </c>
       <c r="C38" t="n">
-        <v>105.048</v>
+        <v>406.872</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001415699772906009</v>
+        <v>0.005586231213783321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106.1318948870807</v>
+        <v>419.2654811182942</v>
       </c>
       <c r="B39" t="n">
-        <v>5896</v>
+        <v>23293</v>
       </c>
       <c r="C39" t="n">
-        <v>106.128</v>
+        <v>419.274</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.003894887080704734</v>
+        <v>0.008518881705811054</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111.7887732684078</v>
+        <v>426.9285261690891</v>
       </c>
       <c r="B40" t="n">
-        <v>6210</v>
+        <v>23718</v>
       </c>
       <c r="C40" t="n">
-        <v>111.78</v>
+        <v>426.924</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.008773268407779256</v>
+        <v>-0.00452616908910386</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112.7096293510222</v>
+        <v>439.327593518597</v>
       </c>
       <c r="B41" t="n">
-        <v>6262</v>
+        <v>24407</v>
       </c>
       <c r="C41" t="n">
-        <v>112.716</v>
+        <v>439.326</v>
       </c>
       <c r="D41" t="n">
-        <v>0.006370648977835458</v>
+        <v>-0.001593518597019283</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112.8740838552614</v>
+        <v>459.3897059189</v>
       </c>
       <c r="B42" t="n">
-        <v>6271</v>
+        <v>25522</v>
       </c>
       <c r="C42" t="n">
-        <v>112.878</v>
+        <v>459.396</v>
       </c>
       <c r="D42" t="n">
-        <v>0.003916144738624894</v>
+        <v>0.006294081100008952</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118.5309622365884</v>
+        <v>471.7887732684078</v>
       </c>
       <c r="B43" t="n">
-        <v>6585</v>
+        <v>26210</v>
       </c>
       <c r="C43" t="n">
-        <v>118.53</v>
+        <v>471.78</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0009622365884212059</v>
+        <v>-0.008773268407821888</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119.4518183192028</v>
+        <v>479.4518183192029</v>
       </c>
       <c r="B44" t="n">
-        <v>6636</v>
+        <v>26636</v>
       </c>
       <c r="C44" t="n">
-        <v>119.448</v>
+        <v>479.448</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.003818319202821385</v>
+        <v>-0.003818319202878229</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125.1086967005299</v>
+        <v>491.8508856687105</v>
       </c>
       <c r="B45" t="n">
-        <v>6950</v>
+        <v>27325</v>
       </c>
       <c r="C45" t="n">
-        <v>125.1</v>
+        <v>491.85</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.008696700529910117</v>
+        <v>-0.0008856687105662786</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125.2731512047691</v>
+        <v>504.2499530182185</v>
       </c>
       <c r="B46" t="n">
-        <v>6960</v>
+        <v>28014</v>
       </c>
       <c r="C46" t="n">
-        <v>125.28</v>
+        <v>504.252</v>
       </c>
       <c r="D46" t="n">
-        <v>0.006848795230894211</v>
+        <v>0.002046981781461454</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126.1940072873835</v>
+        <v>511.9129980690134</v>
       </c>
       <c r="B47" t="n">
-        <v>7011</v>
+        <v>28440</v>
       </c>
       <c r="C47" t="n">
-        <v>126.198</v>
+        <v>511.92</v>
       </c>
       <c r="D47" t="n">
-        <v>0.003992712616494032</v>
+        <v>0.007001930986518801</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131.8508856687106</v>
+        <v>524.3120654185213</v>
       </c>
       <c r="B48" t="n">
-        <v>7325</v>
+        <v>29128</v>
       </c>
       <c r="C48" t="n">
-        <v>131.85</v>
+        <v>524.304</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0008856687105662786</v>
+        <v>-0.008065418521368883</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132.9361962555642</v>
+        <v>531.9751104693166</v>
       </c>
       <c r="B49" t="n">
-        <v>7385</v>
+        <v>29554</v>
       </c>
       <c r="C49" t="n">
-        <v>132.93</v>
+        <v>531.972</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.006196255564162811</v>
+        <v>-0.003110469316652598</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137.5077640500378</v>
+        <v>544.3741778188239</v>
       </c>
       <c r="B50" t="n">
-        <v>7639</v>
+        <v>30243</v>
       </c>
       <c r="C50" t="n">
-        <v>137.502</v>
+        <v>544.374</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.005764050037839752</v>
+        <v>-0.0001778188238859002</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>138.5930746368912</v>
+        <v>556.7732451683321</v>
       </c>
       <c r="B51" t="n">
-        <v>7700</v>
+        <v>30932</v>
       </c>
       <c r="C51" t="n">
-        <v>138.6</v>
+        <v>556.776</v>
       </c>
       <c r="D51" t="n">
-        <v>0.006925363108763349</v>
+        <v>0.002754831667857616</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>144.2499530182185</v>
+        <v>564.4362902191267</v>
       </c>
       <c r="B52" t="n">
-        <v>8014</v>
+        <v>31358</v>
       </c>
       <c r="C52" t="n">
-        <v>144.252</v>
+        <v>564.444</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002046981781489876</v>
+        <v>0.007709780873256022</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>145.1708091008327</v>
+        <v>576.8353575686349</v>
       </c>
       <c r="B53" t="n">
-        <v>8065</v>
+        <v>32046</v>
       </c>
       <c r="C53" t="n">
-        <v>145.17</v>
+        <v>576.828</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0008091008326971405</v>
+        <v>-0.007357568634915879</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>145.3352636050719</v>
+        <v>596.8974699689377</v>
       </c>
       <c r="B54" t="n">
-        <v>8074</v>
+        <v>33161</v>
       </c>
       <c r="C54" t="n">
-        <v>145.332</v>
+        <v>596.898</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.003263605071907705</v>
+        <v>0.0005300310623397309</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>150.9921419863992</v>
+        <v>609.2965373184456</v>
       </c>
       <c r="B55" t="n">
-        <v>8388</v>
+        <v>33850</v>
       </c>
       <c r="C55" t="n">
-        <v>150.984</v>
+        <v>609.3</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.008141986399181178</v>
+        <v>0.00346268155431062</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>151.9129980690134</v>
+        <v>616.9595823692405</v>
       </c>
       <c r="B56" t="n">
-        <v>8440</v>
+        <v>34276</v>
       </c>
       <c r="C56" t="n">
-        <v>151.92</v>
+        <v>616.968</v>
       </c>
       <c r="D56" t="n">
-        <v>0.007001930986632487</v>
+        <v>0.008417630759481654</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>157.5698764503406</v>
+        <v>629.3586497187487</v>
       </c>
       <c r="B57" t="n">
-        <v>8754</v>
+        <v>34964</v>
       </c>
       <c r="C57" t="n">
-        <v>157.572</v>
+        <v>629.352</v>
       </c>
       <c r="D57" t="n">
-        <v>0.002123549659359014</v>
+        <v>-0.006649718748690248</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>157.7343309545799</v>
+        <v>641.7577170682564</v>
       </c>
       <c r="B58" t="n">
-        <v>8763</v>
+        <v>35653</v>
       </c>
       <c r="C58" t="n">
-        <v>157.734</v>
+        <v>641.754</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0003309545798515501</v>
+        <v>-0.003717068256378298</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>158.655187037194</v>
+        <v>649.4207621190513</v>
       </c>
       <c r="B59" t="n">
-        <v>8814</v>
+        <v>36079</v>
       </c>
       <c r="C59" t="n">
-        <v>158.652</v>
+        <v>649.422</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.003187037194038567</v>
+        <v>0.001237880948679049</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>164.3120654185213</v>
+        <v>661.8198294685592</v>
       </c>
       <c r="B60" t="n">
-        <v>9128</v>
+        <v>36768</v>
       </c>
       <c r="C60" t="n">
-        <v>164.304</v>
+        <v>661.824</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.00806541852131204</v>
+        <v>0.004170531440763625</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>165.2329215011359</v>
+        <v>669.4828745193543</v>
       </c>
       <c r="B61" t="n">
-        <v>9180</v>
+        <v>37193</v>
       </c>
       <c r="C61" t="n">
-        <v>165.24</v>
+        <v>669.4739999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0070784988640753</v>
+        <v>-0.008874519354321819</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>165.3973760053747</v>
+        <v>681.881941868862</v>
       </c>
       <c r="B62" t="n">
-        <v>9189</v>
+        <v>37882</v>
       </c>
       <c r="C62" t="n">
-        <v>165.402</v>
+        <v>681.876</v>
       </c>
       <c r="D62" t="n">
-        <v>0.004623994625291061</v>
+        <v>-0.005941868862009869</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>171.054254386702</v>
+        <v>694.2810092183699</v>
       </c>
       <c r="B63" t="n">
-        <v>9503</v>
+        <v>38571</v>
       </c>
       <c r="C63" t="n">
-        <v>171.054</v>
+        <v>694.278</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.000254386701982412</v>
+        <v>-0.003009218369925293</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>171.9751104693166</v>
+        <v>701.9440542691648</v>
       </c>
       <c r="B64" t="n">
-        <v>9554</v>
+        <v>38997</v>
       </c>
       <c r="C64" t="n">
-        <v>171.972</v>
+        <v>701.946</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.003110469316595754</v>
+        <v>0.00194573083524574</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>177.6319888506432</v>
+        <v>714.3431216186727</v>
       </c>
       <c r="B65" t="n">
-        <v>9868</v>
+        <v>39686</v>
       </c>
       <c r="C65" t="n">
-        <v>177.624</v>
+        <v>714.348</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.007988850643215528</v>
+        <v>0.00487838132721663</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>177.7964433548827</v>
+        <v>721.0853105868533</v>
       </c>
       <c r="B66" t="n">
-        <v>9878</v>
+        <v>40060</v>
       </c>
       <c r="C66" t="n">
-        <v>177.804</v>
+        <v>721.0799999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>0.007556645117347216</v>
+        <v>-0.005310586853397581</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>178.7172994374973</v>
+        <v>733.4843779363614</v>
       </c>
       <c r="B67" t="n">
-        <v>9929</v>
+        <v>40749</v>
       </c>
       <c r="C67" t="n">
-        <v>178.722</v>
+        <v>733.482</v>
       </c>
       <c r="D67" t="n">
-        <v>0.004700562502705452</v>
+        <v>-0.002377936361426691</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>184.3741778188239</v>
+        <v>741.1474229871559</v>
       </c>
       <c r="B68" t="n">
-        <v>10243</v>
+        <v>41175</v>
       </c>
       <c r="C68" t="n">
-        <v>184.374</v>
+        <v>741.15</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.0001778188238859002</v>
+        <v>0.002577012844085402</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>185.4594884056779</v>
+        <v>753.5464903366641</v>
       </c>
       <c r="B69" t="n">
-        <v>10303</v>
+        <v>41864</v>
       </c>
       <c r="C69" t="n">
-        <v>185.454</v>
+        <v>753.552</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.00548840567793718</v>
+        <v>0.005509663335942605</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>190.0310562001514</v>
+        <v>761.2095353874588</v>
       </c>
       <c r="B70" t="n">
-        <v>10557</v>
+        <v>42289</v>
       </c>
       <c r="C70" t="n">
-        <v>190.026</v>
+        <v>761.202</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.005056200151415169</v>
+        <v>-0.007535387458801779</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>191.1163667870046</v>
+        <v>773.6086027369669</v>
       </c>
       <c r="B71" t="n">
-        <v>10618</v>
+        <v>42978</v>
       </c>
       <c r="C71" t="n">
-        <v>191.124</v>
+        <v>773.6039999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>0.007633212995443728</v>
+        <v>-0.004602736966944576</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>196.7732451683321</v>
+        <v>786.0076700864748</v>
       </c>
       <c r="B72" t="n">
-        <v>10932</v>
+        <v>43667</v>
       </c>
       <c r="C72" t="n">
-        <v>196.776</v>
+        <v>786.006</v>
       </c>
       <c r="D72" t="n">
-        <v>0.002754831667914459</v>
+        <v>-0.00167008647486</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>197.694101250946</v>
+        <v>793.6707151372698</v>
       </c>
       <c r="B73" t="n">
-        <v>10983</v>
+        <v>44093</v>
       </c>
       <c r="C73" t="n">
-        <v>197.694</v>
+        <v>793.674</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0001012509460167621</v>
+        <v>0.003284862730197347</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>197.8585557551852</v>
+        <v>806.0697824867776</v>
       </c>
       <c r="B74" t="n">
-        <v>10992</v>
+        <v>44782</v>
       </c>
       <c r="C74" t="n">
-        <v>197.856</v>
+        <v>806.076</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.002555755185227326</v>
+        <v>0.00621751322239561</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>203.5154341365127</v>
+        <v>826.1318948870806</v>
       </c>
       <c r="B75" t="n">
-        <v>11306</v>
+        <v>45896</v>
       </c>
       <c r="C75" t="n">
-        <v>203.508</v>
+        <v>826.1279999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.007434136512756595</v>
+        <v>-0.003894887080718945</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>204.4362902191267</v>
+        <v>838.5309622365884</v>
       </c>
       <c r="B76" t="n">
-        <v>11358</v>
+        <v>46585</v>
       </c>
       <c r="C76" t="n">
-        <v>204.444</v>
+        <v>838.53</v>
       </c>
       <c r="D76" t="n">
-        <v>0.007709780873312866</v>
+        <v>-0.000962236588406995</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>210.0931686004542</v>
+        <v>846.1940072873836</v>
       </c>
       <c r="B77" t="n">
-        <v>11672</v>
+        <v>47011</v>
       </c>
       <c r="C77" t="n">
-        <v>210.096</v>
+        <v>846.198</v>
       </c>
       <c r="D77" t="n">
-        <v>0.002831399545812019</v>
+        <v>0.003992712616422978</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>210.2576231046934</v>
+        <v>858.5930746368913</v>
       </c>
       <c r="B78" t="n">
-        <v>11681</v>
+        <v>47700</v>
       </c>
       <c r="C78" t="n">
-        <v>210.258</v>
+        <v>858.6</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0003768953065730329</v>
+        <v>0.006925363108734928</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>211.1784791873073</v>
+        <v>870.9921419863992</v>
       </c>
       <c r="B79" t="n">
-        <v>11732</v>
+        <v>48388</v>
       </c>
       <c r="C79" t="n">
-        <v>211.176</v>
+        <v>870.9839999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.002479187307358188</v>
+        <v>-0.008141986399323287</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>216.8353575686349</v>
+        <v>878.655187037194</v>
       </c>
       <c r="B80" t="n">
-        <v>12046</v>
+        <v>48814</v>
       </c>
       <c r="C80" t="n">
-        <v>216.828</v>
+        <v>878.6519999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.007357568634859035</v>
+        <v>-0.003187037194038567</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>217.920668155488</v>
+        <v>891.054254386702</v>
       </c>
       <c r="B81" t="n">
-        <v>12107</v>
+        <v>49503</v>
       </c>
       <c r="C81" t="n">
-        <v>217.926</v>
+        <v>891.054</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00533184451197144</v>
+        <v>-0.0002543867020676771</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>223.5775465368156</v>
+        <v>898.7172994374972</v>
       </c>
       <c r="B82" t="n">
-        <v>12421</v>
+        <v>49929</v>
       </c>
       <c r="C82" t="n">
-        <v>223.578</v>
+        <v>898.722</v>
       </c>
       <c r="D82" t="n">
-        <v>0.000453463184442171</v>
+        <v>0.004700562502762295</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>230.155281000757</v>
+        <v>911.1163667870045</v>
       </c>
       <c r="B83" t="n">
-        <v>12786</v>
+        <v>50618</v>
       </c>
       <c r="C83" t="n">
-        <v>230.148</v>
+        <v>911.124</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.007281000756989897</v>
+        <v>0.007633212995528993</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>230.3197355049962</v>
+        <v>923.5154341365128</v>
       </c>
       <c r="B84" t="n">
-        <v>12796</v>
+        <v>51306</v>
       </c>
       <c r="C84" t="n">
-        <v>230.328</v>
+        <v>923.5079999999999</v>
       </c>
       <c r="D84" t="n">
-        <v>0.008264495003771799</v>
+        <v>-0.007434136512870282</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>236.8974699689377</v>
+        <v>931.1784791873074</v>
       </c>
       <c r="B85" t="n">
-        <v>13161</v>
+        <v>51732</v>
       </c>
       <c r="C85" t="n">
-        <v>236.898</v>
+        <v>931.1759999999999</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0005300310623113091</v>
+        <v>-0.002479187307471875</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>242.5543483502649</v>
+        <v>943.5775465368156</v>
       </c>
       <c r="B86" t="n">
-        <v>13475</v>
+        <v>52421</v>
       </c>
       <c r="C86" t="n">
-        <v>242.55</v>
+        <v>943.578</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.004348350264962164</v>
+        <v>0.0004534631843853276</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>243.6396589371183</v>
+        <v>963.6396589371184</v>
       </c>
       <c r="B87" t="n">
-        <v>13536</v>
+        <v>53536</v>
       </c>
       <c r="C87" t="n">
-        <v>243.648</v>
+        <v>963.648</v>
       </c>
       <c r="D87" t="n">
-        <v>0.008341062881697781</v>
+        <v>0.008341062881640937</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>249.2965373184456</v>
+        <v>976.0387262866263</v>
       </c>
       <c r="B88" t="n">
-        <v>13850</v>
+        <v>54224</v>
       </c>
       <c r="C88" t="n">
-        <v>249.3</v>
+        <v>976.0319999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>0.003462681554367464</v>
+        <v>-0.006726286626417277</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>250.2173934010598</v>
+        <v>983.7017713374211</v>
       </c>
       <c r="B89" t="n">
-        <v>13901</v>
+        <v>54650</v>
       </c>
       <c r="C89" t="n">
-        <v>250.218</v>
+        <v>983.6999999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0006065989401804472</v>
+        <v>-0.001771337421132557</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>250.381847905299</v>
+        <v>996.1008386869294</v>
       </c>
       <c r="B90" t="n">
-        <v>13910</v>
+        <v>55339</v>
       </c>
       <c r="C90" t="n">
-        <v>250.38</v>
+        <v>996.102</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.001847905299001695</v>
+        <v>0.001161313070610959</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>256.0387262866263</v>
+        <v>1008.499906036437</v>
       </c>
       <c r="B91" t="n">
-        <v>14224</v>
+        <v>56028</v>
       </c>
       <c r="C91" t="n">
-        <v>256.032</v>
+        <v>1008.504</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.00672628662630359</v>
+        <v>0.004093963562922909</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>256.9595823692405</v>
+        <v>1016.162951087232</v>
       </c>
       <c r="B92" t="n">
-        <v>14276</v>
+        <v>56453</v>
       </c>
       <c r="C92" t="n">
-        <v>256.968</v>
+        <v>1016.154</v>
       </c>
       <c r="D92" t="n">
-        <v>0.008417630759538497</v>
+        <v>-0.008951087232048849</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>262.616460750568</v>
+        <v>1028.56201843674</v>
       </c>
       <c r="B93" t="n">
-        <v>14590</v>
+        <v>57142</v>
       </c>
       <c r="C93" t="n">
-        <v>262.62</v>
+        <v>1028.556</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00353924943203765</v>
+        <v>-0.006018436739850586</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>262.780915254807</v>
+        <v>1036.225063487535</v>
       </c>
       <c r="B94" t="n">
-        <v>14599</v>
+        <v>57568</v>
       </c>
       <c r="C94" t="n">
-        <v>262.782</v>
+        <v>1036.224</v>
       </c>
       <c r="D94" t="n">
-        <v>0.001084745192997616</v>
+        <v>-0.001063487534793239</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>263.7017713374211</v>
+        <v>1048.624130837043</v>
       </c>
       <c r="B95" t="n">
-        <v>14650</v>
+        <v>58257</v>
       </c>
       <c r="C95" t="n">
-        <v>263.7</v>
+        <v>1048.626</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.001771337421132557</v>
+        <v>0.001869162957291337</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>269.3586497187487</v>
+        <v>1061.023198186551</v>
       </c>
       <c r="B96" t="n">
-        <v>14964</v>
+        <v>58946</v>
       </c>
       <c r="C96" t="n">
-        <v>269.352</v>
+        <v>1061.028</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.006649718748690248</v>
+        <v>0.004801813449375913</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>270.4439603056018</v>
+        <v>1068.686243237345</v>
       </c>
       <c r="B97" t="n">
-        <v>15025</v>
+        <v>59371</v>
       </c>
       <c r="C97" t="n">
-        <v>270.45</v>
+        <v>1068.678</v>
       </c>
       <c r="D97" t="n">
-        <v>0.006039694398168649</v>
+        <v>-0.008243237345595844</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>275.0155281000757</v>
+        <v>1087.827499555034</v>
       </c>
       <c r="B98" t="n">
-        <v>15279</v>
+        <v>60435</v>
       </c>
       <c r="C98" t="n">
-        <v>275.022</v>
+        <v>1087.83</v>
       </c>
       <c r="D98" t="n">
-        <v>0.006471899924292757</v>
+        <v>0.002500444965789939</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>276.1008386869293</v>
+        <v>1100.226566904542</v>
       </c>
       <c r="B99" t="n">
-        <v>15339</v>
+        <v>61124</v>
       </c>
       <c r="C99" t="n">
-        <v>276.102</v>
+        <v>1100.232</v>
       </c>
       <c r="D99" t="n">
-        <v>0.001161313070667802</v>
+        <v>0.005433095457874515</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>281.7577170682564</v>
+        <v>1107.889611955337</v>
       </c>
       <c r="B100" t="n">
-        <v>15653</v>
+        <v>61549</v>
       </c>
       <c r="C100" t="n">
-        <v>281.754</v>
+        <v>1107.882</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.003717068256378298</v>
+        <v>-0.007611955336642495</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>282.6785731508708</v>
+        <v>1120.288679304845</v>
       </c>
       <c r="B101" t="n">
-        <v>15704</v>
+        <v>62238</v>
       </c>
       <c r="C101" t="n">
-        <v>282.672</v>
+        <v>1120.284</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.006573150870792688</v>
+        <v>-0.004679304845012666</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>282.84302765511</v>
+        <v>1127.951724355639</v>
       </c>
       <c r="B102" t="n">
-        <v>15714</v>
+        <v>62664</v>
       </c>
       <c r="C102" t="n">
-        <v>282.852</v>
+        <v>1127.952</v>
       </c>
       <c r="D102" t="n">
-        <v>0.008972344889969008</v>
+        <v>0.0002756443607268011</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>288.499906036437</v>
+        <v>1140.350791705147</v>
       </c>
       <c r="B103" t="n">
-        <v>16028</v>
+        <v>63353</v>
       </c>
       <c r="C103" t="n">
-        <v>288.504</v>
+        <v>1140.354</v>
       </c>
       <c r="D103" t="n">
-        <v>0.004093963562979752</v>
+        <v>0.003208294852584004</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>289.4207621190515</v>
+        <v>1152.749859054656</v>
       </c>
       <c r="B104" t="n">
-        <v>16079</v>
+        <v>64042</v>
       </c>
       <c r="C104" t="n">
-        <v>289.422</v>
+        <v>1152.756</v>
       </c>
       <c r="D104" t="n">
-        <v>0.001237880948508518</v>
+        <v>0.006140945344213833</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>295.0776405003785</v>
+        <v>1160.41290410545</v>
       </c>
       <c r="B105" t="n">
-        <v>16393</v>
+        <v>64467</v>
       </c>
       <c r="C105" t="n">
-        <v>295.074</v>
+        <v>1160.406</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.003640500378480738</v>
+        <v>-0.006904105450303177</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>295.2420950046177</v>
+        <v>1172.811971454958</v>
       </c>
       <c r="B106" t="n">
-        <v>16402</v>
+        <v>65156</v>
       </c>
       <c r="C106" t="n">
-        <v>295.236</v>
+        <v>1172.808</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.006095004617748145</v>
+        <v>-0.003971454958218601</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>296.1629510872321</v>
+        <v>1192.874083855261</v>
       </c>
       <c r="B107" t="n">
-        <v>16453</v>
+        <v>66271</v>
       </c>
       <c r="C107" t="n">
-        <v>296.154</v>
+        <v>1192.878</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.008951087232105692</v>
+        <v>0.003916144738468574</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>301.8198294685592</v>
+        <v>1205.273151204769</v>
       </c>
       <c r="B108" t="n">
-        <v>16768</v>
+        <v>66960</v>
       </c>
       <c r="C108" t="n">
-        <v>301.824</v>
+        <v>1205.28</v>
       </c>
       <c r="D108" t="n">
-        <v>0.004170531440820469</v>
+        <v>0.006848795231007898</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>302.7406855511736</v>
+        <v>1212.936196255564</v>
       </c>
       <c r="B109" t="n">
-        <v>16819</v>
+        <v>67385</v>
       </c>
       <c r="C109" t="n">
-        <v>302.742</v>
+        <v>1212.93</v>
       </c>
       <c r="D109" t="n">
-        <v>0.001314448826462922</v>
+        <v>-0.006196255564191233</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>302.9051400554128</v>
+        <v>1225.335263605072</v>
       </c>
       <c r="B110" t="n">
-        <v>16828</v>
+        <v>68074</v>
       </c>
       <c r="C110" t="n">
-        <v>302.904</v>
+        <v>1225.332</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.001140055412804486</v>
+        <v>-0.003263605071879283</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>308.5620184367398</v>
+        <v>1237.73433095458</v>
       </c>
       <c r="B111" t="n">
-        <v>17142</v>
+        <v>68763</v>
       </c>
       <c r="C111" t="n">
-        <v>308.556</v>
+        <v>1237.734</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.006018436739850586</v>
+        <v>-0.0003309545797947067</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>309.4828745193543</v>
+        <v>1245.397376005375</v>
       </c>
       <c r="B112" t="n">
-        <v>17193</v>
+        <v>69189</v>
       </c>
       <c r="C112" t="n">
-        <v>309.474</v>
+        <v>1245.402</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.008874519354264976</v>
+        <v>0.00462399462526264</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>315.1397529006813</v>
+        <v>1257.796443354883</v>
       </c>
       <c r="B113" t="n">
-        <v>17508</v>
+        <v>69878</v>
       </c>
       <c r="C113" t="n">
-        <v>315.144</v>
+        <v>1257.804</v>
       </c>
       <c r="D113" t="n">
-        <v>0.004247099318718028</v>
+        <v>0.007556645117347216</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>315.3042074049205</v>
+        <v>1265.459488405678</v>
       </c>
       <c r="B114" t="n">
-        <v>17517</v>
+        <v>70303</v>
       </c>
       <c r="C114" t="n">
-        <v>315.306</v>
+        <v>1265.454</v>
       </c>
       <c r="D114" t="n">
-        <v>0.001792595079450621</v>
+        <v>-0.005488405678079289</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>316.2250634875349</v>
+        <v>1277.858555755185</v>
       </c>
       <c r="B115" t="n">
-        <v>17568</v>
+        <v>70992</v>
       </c>
       <c r="C115" t="n">
-        <v>316.224</v>
+        <v>1277.856</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.001063487534906926</v>
+        <v>-0.002555755185085218</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>321.881941868862</v>
+        <v>1290.257623104693</v>
       </c>
       <c r="B116" t="n">
-        <v>17882</v>
+        <v>71681</v>
       </c>
       <c r="C116" t="n">
-        <v>321.876</v>
+        <v>1290.258</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.005941868862009869</v>
+        <v>0.0003768953065446112</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>322.9672524557156</v>
+        <v>1297.920668155488</v>
       </c>
       <c r="B117" t="n">
-        <v>17943</v>
+        <v>72107</v>
       </c>
       <c r="C117" t="n">
-        <v>322.974</v>
+        <v>1297.926</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00674754428439428</v>
+        <v>0.005331844511829331</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>327.5388202501892</v>
+        <v>1310.319735504996</v>
       </c>
       <c r="B118" t="n">
-        <v>18197</v>
+        <v>72796</v>
       </c>
       <c r="C118" t="n">
-        <v>327.546</v>
+        <v>1310.328</v>
       </c>
       <c r="D118" t="n">
-        <v>0.007179749810745761</v>
+        <v>0.008264495003686534</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>328.6241308370426</v>
+        <v>1330.381847905299</v>
       </c>
       <c r="B119" t="n">
-        <v>18257</v>
+        <v>73910</v>
       </c>
       <c r="C119" t="n">
-        <v>328.626</v>
+        <v>1330.38</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00186916295734818</v>
+        <v>-0.001847905299200647</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>334.2810092183699</v>
+        <v>1342.780915254807</v>
       </c>
       <c r="B120" t="n">
-        <v>18571</v>
+        <v>74599</v>
       </c>
       <c r="C120" t="n">
-        <v>334.278</v>
+        <v>1342.782</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.003009218369982136</v>
+        <v>0.001084745192883929</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>335.2018653009841</v>
+        <v>1350.443960305602</v>
       </c>
       <c r="B121" t="n">
-        <v>18622</v>
+        <v>75025</v>
       </c>
       <c r="C121" t="n">
-        <v>335.196</v>
+        <v>1350.45</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.005865300984112309</v>
+        <v>0.006039694398168649</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>335.3663198052233</v>
+        <v>1362.84302765511</v>
       </c>
       <c r="B122" t="n">
-        <v>18631</v>
+        <v>75714</v>
       </c>
       <c r="C122" t="n">
-        <v>335.358</v>
+        <v>1362.852</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.008319805223322874</v>
+        <v>0.008972344889798478</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>341.0231981865506</v>
+        <v>1375.242095004618</v>
       </c>
       <c r="B123" t="n">
-        <v>18946</v>
+        <v>76402</v>
       </c>
       <c r="C123" t="n">
-        <v>341.028</v>
+        <v>1375.236</v>
       </c>
       <c r="D123" t="n">
-        <v>0.004801813449375913</v>
+        <v>-0.006095004617918676</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>341.9440542691648</v>
+        <v>1382.905140055413</v>
       </c>
       <c r="B124" t="n">
-        <v>18997</v>
+        <v>76828</v>
       </c>
       <c r="C124" t="n">
-        <v>341.946</v>
+        <v>1382.904</v>
       </c>
       <c r="D124" t="n">
-        <v>0.001945730835188897</v>
+        <v>-0.001140055412861329</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>347.600932650492</v>
+        <v>1395.304207404921</v>
       </c>
       <c r="B125" t="n">
-        <v>19311</v>
+        <v>77517</v>
       </c>
       <c r="C125" t="n">
-        <v>347.598</v>
+        <v>1395.306</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.002932650492027733</v>
+        <v>0.001792595079450621</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>347.7653871547313</v>
+        <v>1402.967252455715</v>
       </c>
       <c r="B126" t="n">
-        <v>19320</v>
+        <v>77943</v>
       </c>
       <c r="C126" t="n">
-        <v>347.76</v>
+        <v>1402.974</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.005387154731295141</v>
+        <v>0.006747544284507967</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>348.6862432373454</v>
+        <v>1415.366319805223</v>
       </c>
       <c r="B127" t="n">
-        <v>19371</v>
+        <v>78631</v>
       </c>
       <c r="C127" t="n">
-        <v>348.678</v>
+        <v>1415.358</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.008243237345425314</v>
+        <v>-0.00831980522343656</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>354.3431216186727</v>
+        <v>1427.765387154731</v>
       </c>
       <c r="B128" t="n">
-        <v>19686</v>
+        <v>79320</v>
       </c>
       <c r="C128" t="n">
-        <v>354.348</v>
+        <v>1427.76</v>
       </c>
       <c r="D128" t="n">
-        <v>0.004878381327273473</v>
+        <v>-0.005387154731351984</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>355.4284322055261</v>
+        <v>1435.428432205526</v>
       </c>
       <c r="B129" t="n">
-        <v>19746</v>
+        <v>79746</v>
       </c>
       <c r="C129" t="n">
-        <v>355.428</v>
+        <v>1435.428</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0004322055261241076</v>
+        <v>-0.0004322055260672641</v>
       </c>
     </row>
   </sheetData>
@@ -4078,7 +4078,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>theta_unwrapped_deg</t>
+          <t>theta_monotonic_deg</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -4113,1780 +4113,1780 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794609</v>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.742188968180673</v>
+        <v>20.06211240030279</v>
       </c>
       <c r="B4" t="n">
-        <v>375</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>375</v>
+        <v>1115</v>
       </c>
       <c r="D4" t="n">
-        <v>375</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.663045050794609</v>
+        <v>27.7251574510974</v>
       </c>
       <c r="B5" t="n">
-        <v>426</v>
+        <v>1540</v>
       </c>
       <c r="C5" t="n">
-        <v>426</v>
+        <v>1540</v>
       </c>
       <c r="D5" t="n">
-        <v>426</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.82749955503408</v>
+        <v>40.12422480060559</v>
       </c>
       <c r="B6" t="n">
-        <v>435</v>
+        <v>2229</v>
       </c>
       <c r="C6" t="n">
-        <v>435</v>
+        <v>2229</v>
       </c>
       <c r="D6" t="n">
-        <v>435</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.48437793636135</v>
+        <v>52.52329215011355</v>
       </c>
       <c r="B7" t="n">
-        <v>749</v>
+        <v>2918</v>
       </c>
       <c r="C7" t="n">
-        <v>749</v>
+        <v>2918</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14.40523401897528</v>
+        <v>60.18633720090838</v>
       </c>
       <c r="B8" t="n">
-        <v>800</v>
+        <v>3344</v>
       </c>
       <c r="C8" t="n">
-        <v>800</v>
+        <v>3344</v>
       </c>
       <c r="D8" t="n">
-        <v>800</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20.06211240030279</v>
+        <v>72.58540455041634</v>
       </c>
       <c r="B9" t="n">
-        <v>1115</v>
+        <v>4033</v>
       </c>
       <c r="C9" t="n">
-        <v>1115</v>
+        <v>4033</v>
       </c>
       <c r="D9" t="n">
-        <v>1115</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20.22656690454201</v>
+        <v>92.64751695071936</v>
       </c>
       <c r="B10" t="n">
-        <v>1124</v>
+        <v>5147</v>
       </c>
       <c r="C10" t="n">
-        <v>1124</v>
+        <v>5147</v>
       </c>
       <c r="D10" t="n">
-        <v>1124</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21.14742298715595</v>
+        <v>105.0465843002271</v>
       </c>
       <c r="B11" t="n">
-        <v>1175</v>
+        <v>5836</v>
       </c>
       <c r="C11" t="n">
-        <v>1175</v>
+        <v>5836</v>
       </c>
       <c r="D11" t="n">
-        <v>1175</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26.80430136848346</v>
+        <v>112.7096293510222</v>
       </c>
       <c r="B12" t="n">
-        <v>1489</v>
+        <v>6262</v>
       </c>
       <c r="C12" t="n">
-        <v>1489</v>
+        <v>6262</v>
       </c>
       <c r="D12" t="n">
-        <v>1489</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27.7251574510974</v>
+        <v>125.1086967005299</v>
       </c>
       <c r="B13" t="n">
-        <v>1540</v>
+        <v>6950</v>
       </c>
       <c r="C13" t="n">
-        <v>1540</v>
+        <v>6950</v>
       </c>
       <c r="D13" t="n">
-        <v>1540</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27.88961195533662</v>
+        <v>137.5077640500378</v>
       </c>
       <c r="B14" t="n">
-        <v>1549</v>
+        <v>7639</v>
       </c>
       <c r="C14" t="n">
-        <v>1549</v>
+        <v>7639</v>
       </c>
       <c r="D14" t="n">
-        <v>1549</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33.54649033666414</v>
+        <v>145.1708091008327</v>
       </c>
       <c r="B15" t="n">
-        <v>1864</v>
+        <v>8065</v>
       </c>
       <c r="C15" t="n">
-        <v>1864</v>
+        <v>8065</v>
       </c>
       <c r="D15" t="n">
-        <v>1864</v>
+        <v>8065</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>34.46734641927807</v>
+        <v>157.5698764503406</v>
       </c>
       <c r="B16" t="n">
-        <v>1915</v>
+        <v>8754</v>
       </c>
       <c r="C16" t="n">
-        <v>1915</v>
+        <v>8754</v>
       </c>
       <c r="D16" t="n">
-        <v>1915</v>
+        <v>8754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40.12422480060559</v>
+        <v>165.2329215011359</v>
       </c>
       <c r="B17" t="n">
-        <v>2229</v>
+        <v>9180</v>
       </c>
       <c r="C17" t="n">
-        <v>2229</v>
+        <v>9180</v>
       </c>
       <c r="D17" t="n">
-        <v>2229</v>
+        <v>9180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40.28867930484481</v>
+        <v>177.6319888506432</v>
       </c>
       <c r="B18" t="n">
-        <v>2238</v>
+        <v>9868</v>
       </c>
       <c r="C18" t="n">
-        <v>2238</v>
+        <v>9868</v>
       </c>
       <c r="D18" t="n">
-        <v>2238</v>
+        <v>9868</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41.20953538745874</v>
+        <v>190.0310562001514</v>
       </c>
       <c r="B19" t="n">
-        <v>2289</v>
+        <v>10557</v>
       </c>
       <c r="C19" t="n">
-        <v>2289</v>
+        <v>10557</v>
       </c>
       <c r="D19" t="n">
-        <v>2289</v>
+        <v>10557</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.86641376878626</v>
+        <v>197.694101250946</v>
       </c>
       <c r="B20" t="n">
-        <v>2604</v>
+        <v>10983</v>
       </c>
       <c r="C20" t="n">
-        <v>2604</v>
+        <v>10983</v>
       </c>
       <c r="D20" t="n">
-        <v>2604</v>
+        <v>10983</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47.95172435563941</v>
+        <v>210.0931686004542</v>
       </c>
       <c r="B21" t="n">
-        <v>2664</v>
+        <v>11672</v>
       </c>
       <c r="C21" t="n">
-        <v>2664</v>
+        <v>11672</v>
       </c>
       <c r="D21" t="n">
-        <v>2664</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52.52329215011355</v>
+        <v>230.155281000757</v>
       </c>
       <c r="B22" t="n">
-        <v>2918</v>
+        <v>12786</v>
       </c>
       <c r="C22" t="n">
-        <v>2918</v>
+        <v>12786</v>
       </c>
       <c r="D22" t="n">
-        <v>2918</v>
+        <v>12786</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53.60860273696693</v>
+        <v>242.5543483502649</v>
       </c>
       <c r="B23" t="n">
-        <v>2978</v>
+        <v>13475</v>
       </c>
       <c r="C23" t="n">
-        <v>2978</v>
+        <v>13475</v>
       </c>
       <c r="D23" t="n">
-        <v>2978</v>
+        <v>13475</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59.26548111829421</v>
+        <v>250.2173934010598</v>
       </c>
       <c r="B24" t="n">
-        <v>3293</v>
+        <v>13901</v>
       </c>
       <c r="C24" t="n">
-        <v>3293</v>
+        <v>13901</v>
       </c>
       <c r="D24" t="n">
-        <v>3293</v>
+        <v>13901</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60.18633720090838</v>
+        <v>262.616460750568</v>
       </c>
       <c r="B25" t="n">
-        <v>3344</v>
+        <v>14590</v>
       </c>
       <c r="C25" t="n">
-        <v>3344</v>
+        <v>14590</v>
       </c>
       <c r="D25" t="n">
-        <v>3344</v>
+        <v>14590</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60.35079170514759</v>
+        <v>275.0155281000757</v>
       </c>
       <c r="B26" t="n">
-        <v>3353</v>
+        <v>15279</v>
       </c>
       <c r="C26" t="n">
-        <v>3353</v>
+        <v>15279</v>
       </c>
       <c r="D26" t="n">
-        <v>3353</v>
+        <v>15279</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66.00767008647489</v>
+        <v>282.6785731508708</v>
       </c>
       <c r="B27" t="n">
-        <v>3667</v>
+        <v>15704</v>
       </c>
       <c r="C27" t="n">
-        <v>3667</v>
+        <v>15704</v>
       </c>
       <c r="D27" t="n">
-        <v>3667</v>
+        <v>15704</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66.92852616908905</v>
+        <v>295.0776405003785</v>
       </c>
       <c r="B28" t="n">
-        <v>3718</v>
+        <v>16393</v>
       </c>
       <c r="C28" t="n">
-        <v>3718</v>
+        <v>16393</v>
       </c>
       <c r="D28" t="n">
-        <v>3718</v>
+        <v>16393</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72.58540455041634</v>
+        <v>302.7406855511736</v>
       </c>
       <c r="B29" t="n">
-        <v>4033</v>
+        <v>16819</v>
       </c>
       <c r="C29" t="n">
-        <v>4033</v>
+        <v>16819</v>
       </c>
       <c r="D29" t="n">
-        <v>4033</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>72.74985905465556</v>
+        <v>315.1397529006813</v>
       </c>
       <c r="B30" t="n">
-        <v>4042</v>
+        <v>17508</v>
       </c>
       <c r="C30" t="n">
-        <v>4042</v>
+        <v>17508</v>
       </c>
       <c r="D30" t="n">
-        <v>4042</v>
+        <v>17508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73.67071513726972</v>
+        <v>327.5388202501892</v>
       </c>
       <c r="B31" t="n">
-        <v>4093</v>
+        <v>18197</v>
       </c>
       <c r="C31" t="n">
-        <v>4093</v>
+        <v>18197</v>
       </c>
       <c r="D31" t="n">
-        <v>4093</v>
+        <v>18197</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79.32759351859701</v>
+        <v>335.2018653009841</v>
       </c>
       <c r="B32" t="n">
-        <v>4407</v>
+        <v>18622</v>
       </c>
       <c r="C32" t="n">
-        <v>4407</v>
+        <v>18622</v>
       </c>
       <c r="D32" t="n">
-        <v>4407</v>
+        <v>18622</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80.41290410545039</v>
+        <v>347.600932650492</v>
       </c>
       <c r="B33" t="n">
-        <v>4467</v>
+        <v>19311</v>
       </c>
       <c r="C33" t="n">
-        <v>4467</v>
+        <v>19311</v>
       </c>
       <c r="D33" t="n">
-        <v>4467</v>
+        <v>19311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>86.06978248677768</v>
+        <v>366.7421889681807</v>
       </c>
       <c r="B34" t="n">
-        <v>4782</v>
+        <v>20375</v>
       </c>
       <c r="C34" t="n">
-        <v>4782</v>
+        <v>20375</v>
       </c>
       <c r="D34" t="n">
-        <v>4782</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92.64751695071936</v>
+        <v>374.4052340189753</v>
       </c>
       <c r="B35" t="n">
-        <v>5147</v>
+        <v>20800</v>
       </c>
       <c r="C35" t="n">
-        <v>5147</v>
+        <v>20800</v>
       </c>
       <c r="D35" t="n">
-        <v>5147</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>92.81197145495835</v>
+        <v>386.8043013684834</v>
       </c>
       <c r="B36" t="n">
-        <v>5156</v>
+        <v>21489</v>
       </c>
       <c r="C36" t="n">
-        <v>5156</v>
+        <v>21489</v>
       </c>
       <c r="D36" t="n">
-        <v>5156</v>
+        <v>21489</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99.38970591890003</v>
+        <v>394.467346419278</v>
       </c>
       <c r="B37" t="n">
-        <v>5522</v>
+        <v>21915</v>
       </c>
       <c r="C37" t="n">
-        <v>5522</v>
+        <v>21915</v>
       </c>
       <c r="D37" t="n">
-        <v>5522</v>
+        <v>21915</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105.0465843002271</v>
+        <v>406.8664137687862</v>
       </c>
       <c r="B38" t="n">
-        <v>5836</v>
+        <v>22604</v>
       </c>
       <c r="C38" t="n">
-        <v>5836</v>
+        <v>22604</v>
       </c>
       <c r="D38" t="n">
-        <v>5836</v>
+        <v>22604</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106.1318948870807</v>
+        <v>419.2654811182942</v>
       </c>
       <c r="B39" t="n">
-        <v>5896</v>
+        <v>23293</v>
       </c>
       <c r="C39" t="n">
-        <v>5896</v>
+        <v>23293</v>
       </c>
       <c r="D39" t="n">
-        <v>5896</v>
+        <v>23293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111.7887732684078</v>
+        <v>426.9285261690891</v>
       </c>
       <c r="B40" t="n">
-        <v>6210</v>
+        <v>23718</v>
       </c>
       <c r="C40" t="n">
-        <v>6210</v>
+        <v>23718</v>
       </c>
       <c r="D40" t="n">
-        <v>6210</v>
+        <v>23718</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112.7096293510222</v>
+        <v>439.327593518597</v>
       </c>
       <c r="B41" t="n">
-        <v>6262</v>
+        <v>24407</v>
       </c>
       <c r="C41" t="n">
-        <v>6262</v>
+        <v>24407</v>
       </c>
       <c r="D41" t="n">
-        <v>6262</v>
+        <v>24407</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112.8740838552614</v>
+        <v>459.3897059189</v>
       </c>
       <c r="B42" t="n">
-        <v>6271</v>
+        <v>25522</v>
       </c>
       <c r="C42" t="n">
-        <v>6271</v>
+        <v>25522</v>
       </c>
       <c r="D42" t="n">
-        <v>6271</v>
+        <v>25522</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118.5309622365884</v>
+        <v>471.7887732684078</v>
       </c>
       <c r="B43" t="n">
-        <v>6585</v>
+        <v>26210</v>
       </c>
       <c r="C43" t="n">
-        <v>6585</v>
+        <v>26210</v>
       </c>
       <c r="D43" t="n">
-        <v>6585</v>
+        <v>26210</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119.4518183192028</v>
+        <v>479.4518183192029</v>
       </c>
       <c r="B44" t="n">
-        <v>6636</v>
+        <v>26636</v>
       </c>
       <c r="C44" t="n">
-        <v>6636</v>
+        <v>26636</v>
       </c>
       <c r="D44" t="n">
-        <v>6636</v>
+        <v>26636</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125.1086967005299</v>
+        <v>491.8508856687105</v>
       </c>
       <c r="B45" t="n">
-        <v>6950</v>
+        <v>27325</v>
       </c>
       <c r="C45" t="n">
-        <v>6950</v>
+        <v>27325</v>
       </c>
       <c r="D45" t="n">
-        <v>6950</v>
+        <v>27325</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125.2731512047691</v>
+        <v>504.2499530182185</v>
       </c>
       <c r="B46" t="n">
-        <v>6960</v>
+        <v>28014</v>
       </c>
       <c r="C46" t="n">
-        <v>6960</v>
+        <v>28014</v>
       </c>
       <c r="D46" t="n">
-        <v>6960</v>
+        <v>28014</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126.1940072873835</v>
+        <v>511.9129980690134</v>
       </c>
       <c r="B47" t="n">
-        <v>7011</v>
+        <v>28440</v>
       </c>
       <c r="C47" t="n">
-        <v>7011</v>
+        <v>28440</v>
       </c>
       <c r="D47" t="n">
-        <v>7011</v>
+        <v>28440</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131.8508856687106</v>
+        <v>524.3120654185213</v>
       </c>
       <c r="B48" t="n">
-        <v>7325</v>
+        <v>29128</v>
       </c>
       <c r="C48" t="n">
-        <v>7325</v>
+        <v>29128</v>
       </c>
       <c r="D48" t="n">
-        <v>7325</v>
+        <v>29128</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132.9361962555642</v>
+        <v>531.9751104693166</v>
       </c>
       <c r="B49" t="n">
-        <v>7385</v>
+        <v>29554</v>
       </c>
       <c r="C49" t="n">
-        <v>7385</v>
+        <v>29554</v>
       </c>
       <c r="D49" t="n">
-        <v>7385</v>
+        <v>29554</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137.5077640500378</v>
+        <v>544.3741778188239</v>
       </c>
       <c r="B50" t="n">
-        <v>7639</v>
+        <v>30243</v>
       </c>
       <c r="C50" t="n">
-        <v>7639</v>
+        <v>30243</v>
       </c>
       <c r="D50" t="n">
-        <v>7639</v>
+        <v>30243</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>138.5930746368912</v>
+        <v>556.7732451683321</v>
       </c>
       <c r="B51" t="n">
-        <v>7700</v>
+        <v>30932</v>
       </c>
       <c r="C51" t="n">
-        <v>7700</v>
+        <v>30932</v>
       </c>
       <c r="D51" t="n">
-        <v>7700</v>
+        <v>30932</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>144.2499530182185</v>
+        <v>564.4362902191267</v>
       </c>
       <c r="B52" t="n">
-        <v>8014</v>
+        <v>31358</v>
       </c>
       <c r="C52" t="n">
-        <v>8014</v>
+        <v>31358</v>
       </c>
       <c r="D52" t="n">
-        <v>8014</v>
+        <v>31358</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>145.1708091008327</v>
+        <v>576.8353575686349</v>
       </c>
       <c r="B53" t="n">
-        <v>8065</v>
+        <v>32046</v>
       </c>
       <c r="C53" t="n">
-        <v>8065</v>
+        <v>32046</v>
       </c>
       <c r="D53" t="n">
-        <v>8065</v>
+        <v>32046</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>145.3352636050719</v>
+        <v>596.8974699689377</v>
       </c>
       <c r="B54" t="n">
-        <v>8074</v>
+        <v>33161</v>
       </c>
       <c r="C54" t="n">
-        <v>8074</v>
+        <v>33161</v>
       </c>
       <c r="D54" t="n">
-        <v>8074</v>
+        <v>33161</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>150.9921419863992</v>
+        <v>609.2965373184456</v>
       </c>
       <c r="B55" t="n">
-        <v>8388</v>
+        <v>33850</v>
       </c>
       <c r="C55" t="n">
-        <v>8388</v>
+        <v>33850</v>
       </c>
       <c r="D55" t="n">
-        <v>8388</v>
+        <v>33850</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>151.9129980690134</v>
+        <v>616.9595823692405</v>
       </c>
       <c r="B56" t="n">
-        <v>8440</v>
+        <v>34276</v>
       </c>
       <c r="C56" t="n">
-        <v>8440</v>
+        <v>34276</v>
       </c>
       <c r="D56" t="n">
-        <v>8440</v>
+        <v>34276</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>157.5698764503406</v>
+        <v>629.3586497187487</v>
       </c>
       <c r="B57" t="n">
-        <v>8754</v>
+        <v>34964</v>
       </c>
       <c r="C57" t="n">
-        <v>8754</v>
+        <v>34964</v>
       </c>
       <c r="D57" t="n">
-        <v>8754</v>
+        <v>34964</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>157.7343309545799</v>
+        <v>641.7577170682564</v>
       </c>
       <c r="B58" t="n">
-        <v>8763</v>
+        <v>35653</v>
       </c>
       <c r="C58" t="n">
-        <v>8763</v>
+        <v>35653</v>
       </c>
       <c r="D58" t="n">
-        <v>8763</v>
+        <v>35653</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>158.655187037194</v>
+        <v>649.4207621190513</v>
       </c>
       <c r="B59" t="n">
-        <v>8814</v>
+        <v>36079</v>
       </c>
       <c r="C59" t="n">
-        <v>8814</v>
+        <v>36079</v>
       </c>
       <c r="D59" t="n">
-        <v>8814</v>
+        <v>36079</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>164.3120654185213</v>
+        <v>661.8198294685592</v>
       </c>
       <c r="B60" t="n">
-        <v>9128</v>
+        <v>36768</v>
       </c>
       <c r="C60" t="n">
-        <v>9128</v>
+        <v>36768</v>
       </c>
       <c r="D60" t="n">
-        <v>9128</v>
+        <v>36768</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>165.2329215011359</v>
+        <v>669.4828745193543</v>
       </c>
       <c r="B61" t="n">
-        <v>9180</v>
+        <v>37193</v>
       </c>
       <c r="C61" t="n">
-        <v>9180</v>
+        <v>37193</v>
       </c>
       <c r="D61" t="n">
-        <v>9180</v>
+        <v>37193</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>165.3973760053747</v>
+        <v>681.881941868862</v>
       </c>
       <c r="B62" t="n">
-        <v>9189</v>
+        <v>37882</v>
       </c>
       <c r="C62" t="n">
-        <v>9189</v>
+        <v>37882</v>
       </c>
       <c r="D62" t="n">
-        <v>9189</v>
+        <v>37882</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>171.054254386702</v>
+        <v>694.2810092183699</v>
       </c>
       <c r="B63" t="n">
-        <v>9503</v>
+        <v>38571</v>
       </c>
       <c r="C63" t="n">
-        <v>9503</v>
+        <v>38571</v>
       </c>
       <c r="D63" t="n">
-        <v>9503</v>
+        <v>38571</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>171.9751104693166</v>
+        <v>701.9440542691648</v>
       </c>
       <c r="B64" t="n">
-        <v>9554</v>
+        <v>38997</v>
       </c>
       <c r="C64" t="n">
-        <v>9554</v>
+        <v>38997</v>
       </c>
       <c r="D64" t="n">
-        <v>9554</v>
+        <v>38997</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>177.6319888506432</v>
+        <v>714.3431216186727</v>
       </c>
       <c r="B65" t="n">
-        <v>9868</v>
+        <v>39686</v>
       </c>
       <c r="C65" t="n">
-        <v>9868</v>
+        <v>39686</v>
       </c>
       <c r="D65" t="n">
-        <v>9868</v>
+        <v>39686</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>177.7964433548827</v>
+        <v>721.0853105868533</v>
       </c>
       <c r="B66" t="n">
-        <v>9878</v>
+        <v>40060</v>
       </c>
       <c r="C66" t="n">
-        <v>9878</v>
+        <v>40060</v>
       </c>
       <c r="D66" t="n">
-        <v>9878</v>
+        <v>40060</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>178.7172994374973</v>
+        <v>733.4843779363614</v>
       </c>
       <c r="B67" t="n">
-        <v>9929</v>
+        <v>40749</v>
       </c>
       <c r="C67" t="n">
-        <v>9929</v>
+        <v>40749</v>
       </c>
       <c r="D67" t="n">
-        <v>9929</v>
+        <v>40749</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>184.3741778188239</v>
+        <v>741.1474229871559</v>
       </c>
       <c r="B68" t="n">
-        <v>10243</v>
+        <v>41175</v>
       </c>
       <c r="C68" t="n">
-        <v>10243</v>
+        <v>41175</v>
       </c>
       <c r="D68" t="n">
-        <v>10243</v>
+        <v>41175</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>185.4594884056779</v>
+        <v>753.5464903366641</v>
       </c>
       <c r="B69" t="n">
-        <v>10303</v>
+        <v>41864</v>
       </c>
       <c r="C69" t="n">
-        <v>10303</v>
+        <v>41864</v>
       </c>
       <c r="D69" t="n">
-        <v>10303</v>
+        <v>41864</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>190.0310562001514</v>
+        <v>761.2095353874588</v>
       </c>
       <c r="B70" t="n">
-        <v>10557</v>
+        <v>42289</v>
       </c>
       <c r="C70" t="n">
-        <v>10557</v>
+        <v>42289</v>
       </c>
       <c r="D70" t="n">
-        <v>10557</v>
+        <v>42289</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>191.1163667870046</v>
+        <v>773.6086027369669</v>
       </c>
       <c r="B71" t="n">
-        <v>10618</v>
+        <v>42978</v>
       </c>
       <c r="C71" t="n">
-        <v>10618</v>
+        <v>42978</v>
       </c>
       <c r="D71" t="n">
-        <v>10618</v>
+        <v>42978</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>196.7732451683321</v>
+        <v>786.0076700864748</v>
       </c>
       <c r="B72" t="n">
-        <v>10932</v>
+        <v>43667</v>
       </c>
       <c r="C72" t="n">
-        <v>10932</v>
+        <v>43667</v>
       </c>
       <c r="D72" t="n">
-        <v>10932</v>
+        <v>43667</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>197.694101250946</v>
+        <v>793.6707151372698</v>
       </c>
       <c r="B73" t="n">
-        <v>10983</v>
+        <v>44093</v>
       </c>
       <c r="C73" t="n">
-        <v>10983</v>
+        <v>44093</v>
       </c>
       <c r="D73" t="n">
-        <v>10983</v>
+        <v>44093</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>197.8585557551852</v>
+        <v>806.0697824867776</v>
       </c>
       <c r="B74" t="n">
-        <v>10992</v>
+        <v>44782</v>
       </c>
       <c r="C74" t="n">
-        <v>10992</v>
+        <v>44782</v>
       </c>
       <c r="D74" t="n">
-        <v>10992</v>
+        <v>44782</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>203.5154341365127</v>
+        <v>826.1318948870806</v>
       </c>
       <c r="B75" t="n">
-        <v>11306</v>
+        <v>45896</v>
       </c>
       <c r="C75" t="n">
-        <v>11306</v>
+        <v>45896</v>
       </c>
       <c r="D75" t="n">
-        <v>11306</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>204.4362902191267</v>
+        <v>838.5309622365884</v>
       </c>
       <c r="B76" t="n">
-        <v>11358</v>
+        <v>46585</v>
       </c>
       <c r="C76" t="n">
-        <v>11358</v>
+        <v>46585</v>
       </c>
       <c r="D76" t="n">
-        <v>11358</v>
+        <v>46585</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>210.0931686004542</v>
+        <v>846.1940072873836</v>
       </c>
       <c r="B77" t="n">
-        <v>11672</v>
+        <v>47011</v>
       </c>
       <c r="C77" t="n">
-        <v>11672</v>
+        <v>47011</v>
       </c>
       <c r="D77" t="n">
-        <v>11672</v>
+        <v>47011</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>210.2576231046934</v>
+        <v>858.5930746368913</v>
       </c>
       <c r="B78" t="n">
-        <v>11681</v>
+        <v>47700</v>
       </c>
       <c r="C78" t="n">
-        <v>11681</v>
+        <v>47700</v>
       </c>
       <c r="D78" t="n">
-        <v>11681</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>211.1784791873073</v>
+        <v>870.9921419863992</v>
       </c>
       <c r="B79" t="n">
-        <v>11732</v>
+        <v>48388</v>
       </c>
       <c r="C79" t="n">
-        <v>11732</v>
+        <v>48388</v>
       </c>
       <c r="D79" t="n">
-        <v>11732</v>
+        <v>48388</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>216.8353575686349</v>
+        <v>878.655187037194</v>
       </c>
       <c r="B80" t="n">
-        <v>12046</v>
+        <v>48814</v>
       </c>
       <c r="C80" t="n">
-        <v>12046</v>
+        <v>48814</v>
       </c>
       <c r="D80" t="n">
-        <v>12046</v>
+        <v>48814</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>217.920668155488</v>
+        <v>891.054254386702</v>
       </c>
       <c r="B81" t="n">
-        <v>12107</v>
+        <v>49503</v>
       </c>
       <c r="C81" t="n">
-        <v>12107</v>
+        <v>49503</v>
       </c>
       <c r="D81" t="n">
-        <v>12107</v>
+        <v>49503</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>223.5775465368156</v>
+        <v>898.7172994374972</v>
       </c>
       <c r="B82" t="n">
-        <v>12421</v>
+        <v>49929</v>
       </c>
       <c r="C82" t="n">
-        <v>12421</v>
+        <v>49929</v>
       </c>
       <c r="D82" t="n">
-        <v>12421</v>
+        <v>49929</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>230.155281000757</v>
+        <v>911.1163667870045</v>
       </c>
       <c r="B83" t="n">
-        <v>12786</v>
+        <v>50618</v>
       </c>
       <c r="C83" t="n">
-        <v>12786</v>
+        <v>50618</v>
       </c>
       <c r="D83" t="n">
-        <v>12786</v>
+        <v>50618</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>230.3197355049962</v>
+        <v>923.5154341365128</v>
       </c>
       <c r="B84" t="n">
-        <v>12796</v>
+        <v>51306</v>
       </c>
       <c r="C84" t="n">
-        <v>12796</v>
+        <v>51306</v>
       </c>
       <c r="D84" t="n">
-        <v>12796</v>
+        <v>51306</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>236.8974699689377</v>
+        <v>931.1784791873074</v>
       </c>
       <c r="B85" t="n">
-        <v>13161</v>
+        <v>51732</v>
       </c>
       <c r="C85" t="n">
-        <v>13161</v>
+        <v>51732</v>
       </c>
       <c r="D85" t="n">
-        <v>13161</v>
+        <v>51732</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>242.5543483502649</v>
+        <v>943.5775465368156</v>
       </c>
       <c r="B86" t="n">
-        <v>13475</v>
+        <v>52421</v>
       </c>
       <c r="C86" t="n">
-        <v>13475</v>
+        <v>52421</v>
       </c>
       <c r="D86" t="n">
-        <v>13475</v>
+        <v>52421</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>243.6396589371183</v>
+        <v>963.6396589371184</v>
       </c>
       <c r="B87" t="n">
-        <v>13536</v>
+        <v>53536</v>
       </c>
       <c r="C87" t="n">
-        <v>13536</v>
+        <v>53536</v>
       </c>
       <c r="D87" t="n">
-        <v>13536</v>
+        <v>53536</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>249.2965373184456</v>
+        <v>976.0387262866263</v>
       </c>
       <c r="B88" t="n">
-        <v>13850</v>
+        <v>54224</v>
       </c>
       <c r="C88" t="n">
-        <v>13850</v>
+        <v>54224</v>
       </c>
       <c r="D88" t="n">
-        <v>13850</v>
+        <v>54224</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>250.2173934010598</v>
+        <v>983.7017713374211</v>
       </c>
       <c r="B89" t="n">
-        <v>13901</v>
+        <v>54650</v>
       </c>
       <c r="C89" t="n">
-        <v>13901</v>
+        <v>54650</v>
       </c>
       <c r="D89" t="n">
-        <v>13901</v>
+        <v>54650</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>250.381847905299</v>
+        <v>996.1008386869294</v>
       </c>
       <c r="B90" t="n">
-        <v>13910</v>
+        <v>55339</v>
       </c>
       <c r="C90" t="n">
-        <v>13910</v>
+        <v>55339</v>
       </c>
       <c r="D90" t="n">
-        <v>13910</v>
+        <v>55339</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>256.0387262866263</v>
+        <v>1008.499906036437</v>
       </c>
       <c r="B91" t="n">
-        <v>14224</v>
+        <v>56028</v>
       </c>
       <c r="C91" t="n">
-        <v>14224</v>
+        <v>56028</v>
       </c>
       <c r="D91" t="n">
-        <v>14224</v>
+        <v>56028</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>256.9595823692405</v>
+        <v>1016.162951087232</v>
       </c>
       <c r="B92" t="n">
-        <v>14276</v>
+        <v>56453</v>
       </c>
       <c r="C92" t="n">
-        <v>14276</v>
+        <v>56453</v>
       </c>
       <c r="D92" t="n">
-        <v>14276</v>
+        <v>56453</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>262.616460750568</v>
+        <v>1028.56201843674</v>
       </c>
       <c r="B93" t="n">
-        <v>14590</v>
+        <v>57142</v>
       </c>
       <c r="C93" t="n">
-        <v>14590</v>
+        <v>57142</v>
       </c>
       <c r="D93" t="n">
-        <v>14590</v>
+        <v>57142</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>262.780915254807</v>
+        <v>1036.225063487535</v>
       </c>
       <c r="B94" t="n">
-        <v>14599</v>
+        <v>57568</v>
       </c>
       <c r="C94" t="n">
-        <v>14599</v>
+        <v>57568</v>
       </c>
       <c r="D94" t="n">
-        <v>14599</v>
+        <v>57568</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>263.7017713374211</v>
+        <v>1048.624130837043</v>
       </c>
       <c r="B95" t="n">
-        <v>14650</v>
+        <v>58257</v>
       </c>
       <c r="C95" t="n">
-        <v>14650</v>
+        <v>58257</v>
       </c>
       <c r="D95" t="n">
-        <v>14650</v>
+        <v>58257</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>269.3586497187487</v>
+        <v>1061.023198186551</v>
       </c>
       <c r="B96" t="n">
-        <v>14964</v>
+        <v>58946</v>
       </c>
       <c r="C96" t="n">
-        <v>14964</v>
+        <v>58946</v>
       </c>
       <c r="D96" t="n">
-        <v>14964</v>
+        <v>58946</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>270.4439603056018</v>
+        <v>1068.686243237345</v>
       </c>
       <c r="B97" t="n">
-        <v>15025</v>
+        <v>59371</v>
       </c>
       <c r="C97" t="n">
-        <v>15025</v>
+        <v>59371</v>
       </c>
       <c r="D97" t="n">
-        <v>15025</v>
+        <v>59371</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>275.0155281000757</v>
+        <v>1087.827499555034</v>
       </c>
       <c r="B98" t="n">
-        <v>15279</v>
+        <v>60435</v>
       </c>
       <c r="C98" t="n">
-        <v>15279</v>
+        <v>60435</v>
       </c>
       <c r="D98" t="n">
-        <v>15279</v>
+        <v>60435</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>276.1008386869293</v>
+        <v>1100.226566904542</v>
       </c>
       <c r="B99" t="n">
-        <v>15339</v>
+        <v>61124</v>
       </c>
       <c r="C99" t="n">
-        <v>15339</v>
+        <v>61124</v>
       </c>
       <c r="D99" t="n">
-        <v>15339</v>
+        <v>61124</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>281.7577170682564</v>
+        <v>1107.889611955337</v>
       </c>
       <c r="B100" t="n">
-        <v>15653</v>
+        <v>61549</v>
       </c>
       <c r="C100" t="n">
-        <v>15653</v>
+        <v>61549</v>
       </c>
       <c r="D100" t="n">
-        <v>15653</v>
+        <v>61549</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>282.6785731508708</v>
+        <v>1120.288679304845</v>
       </c>
       <c r="B101" t="n">
-        <v>15704</v>
+        <v>62238</v>
       </c>
       <c r="C101" t="n">
-        <v>15704</v>
+        <v>62238</v>
       </c>
       <c r="D101" t="n">
-        <v>15704</v>
+        <v>62238</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>282.84302765511</v>
+        <v>1127.951724355639</v>
       </c>
       <c r="B102" t="n">
-        <v>15714</v>
+        <v>62664</v>
       </c>
       <c r="C102" t="n">
-        <v>15714</v>
+        <v>62664</v>
       </c>
       <c r="D102" t="n">
-        <v>15714</v>
+        <v>62664</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>288.499906036437</v>
+        <v>1140.350791705147</v>
       </c>
       <c r="B103" t="n">
-        <v>16028</v>
+        <v>63353</v>
       </c>
       <c r="C103" t="n">
-        <v>16028</v>
+        <v>63353</v>
       </c>
       <c r="D103" t="n">
-        <v>16028</v>
+        <v>63353</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>289.4207621190515</v>
+        <v>1152.749859054656</v>
       </c>
       <c r="B104" t="n">
-        <v>16079</v>
+        <v>64042</v>
       </c>
       <c r="C104" t="n">
-        <v>16079</v>
+        <v>64042</v>
       </c>
       <c r="D104" t="n">
-        <v>16079</v>
+        <v>64042</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>295.0776405003785</v>
+        <v>1160.41290410545</v>
       </c>
       <c r="B105" t="n">
-        <v>16393</v>
+        <v>64467</v>
       </c>
       <c r="C105" t="n">
-        <v>16393</v>
+        <v>64467</v>
       </c>
       <c r="D105" t="n">
-        <v>16393</v>
+        <v>64467</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>295.2420950046177</v>
+        <v>1172.811971454958</v>
       </c>
       <c r="B106" t="n">
-        <v>16402</v>
+        <v>65156</v>
       </c>
       <c r="C106" t="n">
-        <v>16402</v>
+        <v>65156</v>
       </c>
       <c r="D106" t="n">
-        <v>16402</v>
+        <v>65156</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>296.1629510872321</v>
+        <v>1192.874083855261</v>
       </c>
       <c r="B107" t="n">
-        <v>16453</v>
+        <v>66271</v>
       </c>
       <c r="C107" t="n">
-        <v>16453</v>
+        <v>66271</v>
       </c>
       <c r="D107" t="n">
-        <v>16453</v>
+        <v>66271</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>301.8198294685592</v>
+        <v>1205.273151204769</v>
       </c>
       <c r="B108" t="n">
-        <v>16768</v>
+        <v>66960</v>
       </c>
       <c r="C108" t="n">
-        <v>16768</v>
+        <v>66960</v>
       </c>
       <c r="D108" t="n">
-        <v>16768</v>
+        <v>66960</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>302.7406855511736</v>
+        <v>1212.936196255564</v>
       </c>
       <c r="B109" t="n">
-        <v>16819</v>
+        <v>67385</v>
       </c>
       <c r="C109" t="n">
-        <v>16819</v>
+        <v>67385</v>
       </c>
       <c r="D109" t="n">
-        <v>16819</v>
+        <v>67385</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>302.9051400554128</v>
+        <v>1225.335263605072</v>
       </c>
       <c r="B110" t="n">
-        <v>16828</v>
+        <v>68074</v>
       </c>
       <c r="C110" t="n">
-        <v>16828</v>
+        <v>68074</v>
       </c>
       <c r="D110" t="n">
-        <v>16828</v>
+        <v>68074</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>308.5620184367398</v>
+        <v>1237.73433095458</v>
       </c>
       <c r="B111" t="n">
-        <v>17142</v>
+        <v>68763</v>
       </c>
       <c r="C111" t="n">
-        <v>17142</v>
+        <v>68763</v>
       </c>
       <c r="D111" t="n">
-        <v>17142</v>
+        <v>68763</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>309.4828745193543</v>
+        <v>1245.397376005375</v>
       </c>
       <c r="B112" t="n">
-        <v>17193</v>
+        <v>69189</v>
       </c>
       <c r="C112" t="n">
-        <v>17193</v>
+        <v>69189</v>
       </c>
       <c r="D112" t="n">
-        <v>17193</v>
+        <v>69189</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>315.1397529006813</v>
+        <v>1257.796443354883</v>
       </c>
       <c r="B113" t="n">
-        <v>17508</v>
+        <v>69878</v>
       </c>
       <c r="C113" t="n">
-        <v>17508</v>
+        <v>69878</v>
       </c>
       <c r="D113" t="n">
-        <v>17508</v>
+        <v>69878</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>315.3042074049205</v>
+        <v>1265.459488405678</v>
       </c>
       <c r="B114" t="n">
-        <v>17517</v>
+        <v>70303</v>
       </c>
       <c r="C114" t="n">
-        <v>17517</v>
+        <v>70303</v>
       </c>
       <c r="D114" t="n">
-        <v>17517</v>
+        <v>70303</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>316.2250634875349</v>
+        <v>1277.858555755185</v>
       </c>
       <c r="B115" t="n">
-        <v>17568</v>
+        <v>70992</v>
       </c>
       <c r="C115" t="n">
-        <v>17568</v>
+        <v>70992</v>
       </c>
       <c r="D115" t="n">
-        <v>17568</v>
+        <v>70992</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>321.881941868862</v>
+        <v>1290.257623104693</v>
       </c>
       <c r="B116" t="n">
-        <v>17882</v>
+        <v>71681</v>
       </c>
       <c r="C116" t="n">
-        <v>17882</v>
+        <v>71681</v>
       </c>
       <c r="D116" t="n">
-        <v>17882</v>
+        <v>71681</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>322.9672524557156</v>
+        <v>1297.920668155488</v>
       </c>
       <c r="B117" t="n">
-        <v>17943</v>
+        <v>72107</v>
       </c>
       <c r="C117" t="n">
-        <v>17943</v>
+        <v>72107</v>
       </c>
       <c r="D117" t="n">
-        <v>17943</v>
+        <v>72107</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>327.5388202501892</v>
+        <v>1310.319735504996</v>
       </c>
       <c r="B118" t="n">
-        <v>18197</v>
+        <v>72796</v>
       </c>
       <c r="C118" t="n">
-        <v>18197</v>
+        <v>72796</v>
       </c>
       <c r="D118" t="n">
-        <v>18197</v>
+        <v>72796</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>328.6241308370426</v>
+        <v>1330.381847905299</v>
       </c>
       <c r="B119" t="n">
-        <v>18257</v>
+        <v>73910</v>
       </c>
       <c r="C119" t="n">
-        <v>18257</v>
+        <v>73910</v>
       </c>
       <c r="D119" t="n">
-        <v>18257</v>
+        <v>73910</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>334.2810092183699</v>
+        <v>1342.780915254807</v>
       </c>
       <c r="B120" t="n">
-        <v>18571</v>
+        <v>74599</v>
       </c>
       <c r="C120" t="n">
-        <v>18571</v>
+        <v>74599</v>
       </c>
       <c r="D120" t="n">
-        <v>18571</v>
+        <v>74599</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>335.2018653009841</v>
+        <v>1350.443960305602</v>
       </c>
       <c r="B121" t="n">
-        <v>18622</v>
+        <v>75025</v>
       </c>
       <c r="C121" t="n">
-        <v>18622</v>
+        <v>75025</v>
       </c>
       <c r="D121" t="n">
-        <v>18622</v>
+        <v>75025</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>335.3663198052233</v>
+        <v>1362.84302765511</v>
       </c>
       <c r="B122" t="n">
-        <v>18631</v>
+        <v>75714</v>
       </c>
       <c r="C122" t="n">
-        <v>18631</v>
+        <v>75714</v>
       </c>
       <c r="D122" t="n">
-        <v>18631</v>
+        <v>75714</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>341.0231981865506</v>
+        <v>1375.242095004618</v>
       </c>
       <c r="B123" t="n">
-        <v>18946</v>
+        <v>76402</v>
       </c>
       <c r="C123" t="n">
-        <v>18946</v>
+        <v>76402</v>
       </c>
       <c r="D123" t="n">
-        <v>18946</v>
+        <v>76402</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>341.9440542691648</v>
+        <v>1382.905140055413</v>
       </c>
       <c r="B124" t="n">
-        <v>18997</v>
+        <v>76828</v>
       </c>
       <c r="C124" t="n">
-        <v>18997</v>
+        <v>76828</v>
       </c>
       <c r="D124" t="n">
-        <v>18997</v>
+        <v>76828</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>347.600932650492</v>
+        <v>1395.304207404921</v>
       </c>
       <c r="B125" t="n">
-        <v>19311</v>
+        <v>77517</v>
       </c>
       <c r="C125" t="n">
-        <v>19311</v>
+        <v>77517</v>
       </c>
       <c r="D125" t="n">
-        <v>19311</v>
+        <v>77517</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>347.7653871547313</v>
+        <v>1402.967252455715</v>
       </c>
       <c r="B126" t="n">
-        <v>19320</v>
+        <v>77943</v>
       </c>
       <c r="C126" t="n">
-        <v>19320</v>
+        <v>77943</v>
       </c>
       <c r="D126" t="n">
-        <v>19320</v>
+        <v>77943</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>348.6862432373454</v>
+        <v>1415.366319805223</v>
       </c>
       <c r="B127" t="n">
-        <v>19371</v>
+        <v>78631</v>
       </c>
       <c r="C127" t="n">
-        <v>19371</v>
+        <v>78631</v>
       </c>
       <c r="D127" t="n">
-        <v>19371</v>
+        <v>78631</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>354.3431216186727</v>
+        <v>1427.765387154731</v>
       </c>
       <c r="B128" t="n">
-        <v>19686</v>
+        <v>79320</v>
       </c>
       <c r="C128" t="n">
-        <v>19686</v>
+        <v>79320</v>
       </c>
       <c r="D128" t="n">
-        <v>19686</v>
+        <v>79320</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>355.4284322055261</v>
+        <v>1435.428432205526</v>
       </c>
       <c r="B129" t="n">
-        <v>19746</v>
+        <v>79746</v>
       </c>
       <c r="C129" t="n">
-        <v>19746</v>
+        <v>79746</v>
       </c>
       <c r="D129" t="n">
-        <v>19746</v>
+        <v>79746</v>
       </c>
     </row>
   </sheetData>
@@ -5933,10 +5933,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794609</v>
       </c>
       <c r="D2" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794609</v>
       </c>
     </row>
     <row r="3">
@@ -5944,13 +5944,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794609</v>
       </c>
       <c r="C3" t="n">
-        <v>6.742188968180673</v>
+        <v>20.06211240030279</v>
       </c>
       <c r="D3" t="n">
-        <v>5.656878381327291</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="4">
@@ -5958,13 +5958,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.742188968180673</v>
+        <v>20.06211240030279</v>
       </c>
       <c r="C4" t="n">
-        <v>7.663045050794609</v>
+        <v>27.7251574510974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9208560826139358</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="5">
@@ -5972,13 +5972,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.663045050794609</v>
+        <v>27.7251574510974</v>
       </c>
       <c r="C5" t="n">
-        <v>7.82749955503408</v>
+        <v>40.12422480060559</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1644545042394716</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="6">
@@ -5986,13 +5986,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.82749955503408</v>
+        <v>40.12422480060559</v>
       </c>
       <c r="C6" t="n">
-        <v>13.48437793636135</v>
+        <v>52.52329215011355</v>
       </c>
       <c r="D6" t="n">
-        <v>5.656878381327266</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="7">
@@ -6000,13 +6000,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48437793636135</v>
+        <v>52.52329215011355</v>
       </c>
       <c r="C7" t="n">
-        <v>14.40523401897528</v>
+        <v>60.18633720090838</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9208560826139323</v>
+        <v>7.663045050794828</v>
       </c>
     </row>
     <row r="8">
@@ -6014,13 +6014,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.40523401897528</v>
+        <v>60.18633720090838</v>
       </c>
       <c r="C8" t="n">
-        <v>20.06211240030279</v>
+        <v>72.58540455041634</v>
       </c>
       <c r="D8" t="n">
-        <v>5.656878381327516</v>
+        <v>12.39906734950797</v>
       </c>
     </row>
     <row r="9">
@@ -6028,13 +6028,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.06211240030279</v>
+        <v>72.58540455041634</v>
       </c>
       <c r="C9" t="n">
-        <v>20.22656690454201</v>
+        <v>92.64751695071936</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1644545042392203</v>
+        <v>20.06211240030302</v>
       </c>
     </row>
     <row r="10">
@@ -6042,13 +6042,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20.22656690454201</v>
+        <v>92.64751695071936</v>
       </c>
       <c r="C10" t="n">
-        <v>21.14742298715595</v>
+        <v>105.0465843002271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="11">
@@ -6056,13 +6056,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21.14742298715595</v>
+        <v>105.0465843002271</v>
       </c>
       <c r="C11" t="n">
-        <v>26.80430136848346</v>
+        <v>112.7096293510222</v>
       </c>
       <c r="D11" t="n">
-        <v>5.656878381327513</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="12">
@@ -6070,13 +6070,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26.80430136848346</v>
+        <v>112.7096293510222</v>
       </c>
       <c r="C12" t="n">
-        <v>27.7251574510974</v>
+        <v>125.1086967005299</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950775</v>
       </c>
     </row>
     <row r="13">
@@ -6084,13 +6084,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27.7251574510974</v>
+        <v>125.1086967005299</v>
       </c>
       <c r="C13" t="n">
-        <v>27.88961195533662</v>
+        <v>137.5077640500378</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1644545042392203</v>
+        <v>12.39906734950794</v>
       </c>
     </row>
     <row r="14">
@@ -6098,13 +6098,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27.88961195533662</v>
+        <v>137.5077640500378</v>
       </c>
       <c r="C14" t="n">
-        <v>33.54649033666414</v>
+        <v>145.1708091008327</v>
       </c>
       <c r="D14" t="n">
-        <v>5.656878381327513</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="15">
@@ -6112,13 +6112,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>33.54649033666414</v>
+        <v>145.1708091008327</v>
       </c>
       <c r="C15" t="n">
-        <v>34.46734641927807</v>
+        <v>157.5698764503406</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="16">
@@ -6126,13 +6126,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>34.46734641927807</v>
+        <v>157.5698764503406</v>
       </c>
       <c r="C16" t="n">
-        <v>40.12422480060559</v>
+        <v>165.2329215011359</v>
       </c>
       <c r="D16" t="n">
-        <v>5.656878381327516</v>
+        <v>7.66304505079529</v>
       </c>
     </row>
     <row r="17">
@@ -6140,13 +6140,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>40.12422480060559</v>
+        <v>165.2329215011359</v>
       </c>
       <c r="C17" t="n">
-        <v>40.28867930484481</v>
+        <v>177.6319888506432</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950728</v>
       </c>
     </row>
     <row r="18">
@@ -6154,13 +6154,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>40.28867930484481</v>
+        <v>177.6319888506432</v>
       </c>
       <c r="C18" t="n">
-        <v>41.20953538745874</v>
+        <v>190.0310562001514</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="19">
@@ -6168,13 +6168,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41.20953538745874</v>
+        <v>190.0310562001514</v>
       </c>
       <c r="C19" t="n">
-        <v>46.86641376878626</v>
+        <v>197.694101250946</v>
       </c>
       <c r="D19" t="n">
-        <v>5.656878381327516</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="20">
@@ -6182,13 +6182,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>46.86641376878626</v>
+        <v>197.694101250946</v>
       </c>
       <c r="C20" t="n">
-        <v>47.95172435563941</v>
+        <v>210.0931686004542</v>
       </c>
       <c r="D20" t="n">
-        <v>1.085310586853154</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="21">
@@ -6196,13 +6196,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>47.95172435563941</v>
+        <v>210.0931686004542</v>
       </c>
       <c r="C21" t="n">
-        <v>52.52329215011355</v>
+        <v>230.155281000757</v>
       </c>
       <c r="D21" t="n">
-        <v>4.571567794474134</v>
+        <v>20.06211240030279</v>
       </c>
     </row>
     <row r="22">
@@ -6210,13 +6210,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>52.52329215011355</v>
+        <v>230.155281000757</v>
       </c>
       <c r="C22" t="n">
-        <v>53.60860273696693</v>
+        <v>242.5543483502649</v>
       </c>
       <c r="D22" t="n">
-        <v>1.085310586853382</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="23">
@@ -6224,13 +6224,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>53.60860273696693</v>
+        <v>242.5543483502649</v>
       </c>
       <c r="C23" t="n">
-        <v>59.26548111829421</v>
+        <v>250.2173934010598</v>
       </c>
       <c r="D23" t="n">
-        <v>5.656878381327282</v>
+        <v>7.663045050794864</v>
       </c>
     </row>
     <row r="24">
@@ -6238,13 +6238,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>59.26548111829421</v>
+        <v>250.2173934010598</v>
       </c>
       <c r="C24" t="n">
-        <v>60.18633720090838</v>
+        <v>262.616460750568</v>
       </c>
       <c r="D24" t="n">
-        <v>0.920856082614165</v>
+        <v>12.39906734950816</v>
       </c>
     </row>
     <row r="25">
@@ -6252,13 +6252,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>60.18633720090838</v>
+        <v>262.616460750568</v>
       </c>
       <c r="C25" t="n">
-        <v>60.35079170514759</v>
+        <v>275.0155281000757</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="26">
@@ -6266,13 +6266,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>60.35079170514759</v>
+        <v>275.0155281000757</v>
       </c>
       <c r="C26" t="n">
-        <v>66.00767008647489</v>
+        <v>282.6785731508708</v>
       </c>
       <c r="D26" t="n">
-        <v>5.656878381327296</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="27">
@@ -6280,13 +6280,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>66.00767008647489</v>
+        <v>282.6785731508708</v>
       </c>
       <c r="C27" t="n">
-        <v>66.92852616908905</v>
+        <v>295.0776405003785</v>
       </c>
       <c r="D27" t="n">
-        <v>0.920856082614165</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="28">
@@ -6294,13 +6294,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>66.92852616908905</v>
+        <v>295.0776405003785</v>
       </c>
       <c r="C28" t="n">
-        <v>72.58540455041634</v>
+        <v>302.7406855511736</v>
       </c>
       <c r="D28" t="n">
-        <v>5.656878381327289</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="29">
@@ -6308,13 +6308,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>72.58540455041634</v>
+        <v>302.7406855511736</v>
       </c>
       <c r="C29" t="n">
-        <v>72.74985905465556</v>
+        <v>315.1397529006813</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="30">
@@ -6322,13 +6322,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>72.74985905465556</v>
+        <v>315.1397529006813</v>
       </c>
       <c r="C30" t="n">
-        <v>73.67071513726972</v>
+        <v>327.5388202501892</v>
       </c>
       <c r="D30" t="n">
-        <v>0.920856082614165</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="31">
@@ -6336,13 +6336,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>73.67071513726972</v>
+        <v>327.5388202501892</v>
       </c>
       <c r="C31" t="n">
-        <v>79.32759351859701</v>
+        <v>335.2018653009841</v>
       </c>
       <c r="D31" t="n">
-        <v>5.656878381327289</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="32">
@@ -6350,13 +6350,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>79.32759351859701</v>
+        <v>335.2018653009841</v>
       </c>
       <c r="C32" t="n">
-        <v>80.41290410545039</v>
+        <v>347.600932650492</v>
       </c>
       <c r="D32" t="n">
-        <v>1.085310586853382</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="33">
@@ -6364,13 +6364,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>80.41290410545039</v>
+        <v>347.600932650492</v>
       </c>
       <c r="C33" t="n">
-        <v>86.06978248677768</v>
+        <v>366.7421889681807</v>
       </c>
       <c r="D33" t="n">
-        <v>5.656878381327289</v>
+        <v>19.14125631768866</v>
       </c>
     </row>
     <row r="34">
@@ -6378,13 +6378,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>86.06978248677768</v>
+        <v>366.7421889681807</v>
       </c>
       <c r="C34" t="n">
-        <v>92.64751695071936</v>
+        <v>374.4052340189753</v>
       </c>
       <c r="D34" t="n">
-        <v>6.577734463941681</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="35">
@@ -6392,13 +6392,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>92.64751695071936</v>
+        <v>374.4052340189753</v>
       </c>
       <c r="C35" t="n">
-        <v>92.81197145495835</v>
+        <v>386.8043013684834</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1644545042389893</v>
+        <v>12.39906734950813</v>
       </c>
     </row>
     <row r="36">
@@ -6406,13 +6406,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>92.81197145495835</v>
+        <v>386.8043013684834</v>
       </c>
       <c r="C36" t="n">
-        <v>99.38970591890003</v>
+        <v>394.467346419278</v>
       </c>
       <c r="D36" t="n">
-        <v>6.577734463941681</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="37">
@@ -6420,13 +6420,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>99.38970591890003</v>
+        <v>394.467346419278</v>
       </c>
       <c r="C37" t="n">
-        <v>105.0465843002271</v>
+        <v>406.8664137687862</v>
       </c>
       <c r="D37" t="n">
-        <v>5.656878381327061</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="38">
@@ -6434,13 +6434,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>105.0465843002271</v>
+        <v>406.8664137687862</v>
       </c>
       <c r="C38" t="n">
-        <v>106.1318948870807</v>
+        <v>419.2654811182942</v>
       </c>
       <c r="D38" t="n">
-        <v>1.085310586853609</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="39">
@@ -6448,13 +6448,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>106.1318948870807</v>
+        <v>419.2654811182942</v>
       </c>
       <c r="C39" t="n">
-        <v>111.7887732684078</v>
+        <v>426.9285261690891</v>
       </c>
       <c r="D39" t="n">
-        <v>5.656878381327076</v>
+        <v>7.663045050794892</v>
       </c>
     </row>
     <row r="40">
@@ -6462,13 +6462,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>111.7887732684078</v>
+        <v>426.9285261690891</v>
       </c>
       <c r="C40" t="n">
-        <v>112.7096293510222</v>
+        <v>439.327593518597</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9208560826143781</v>
+        <v>12.3990673495079</v>
       </c>
     </row>
     <row r="41">
@@ -6476,13 +6476,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>112.7096293510222</v>
+        <v>439.327593518597</v>
       </c>
       <c r="C41" t="n">
-        <v>112.8740838552614</v>
+        <v>459.3897059189</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1644545042392167</v>
+        <v>20.06211240030302</v>
       </c>
     </row>
     <row r="42">
@@ -6490,13 +6490,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>112.8740838552614</v>
+        <v>459.3897059189</v>
       </c>
       <c r="C42" t="n">
-        <v>118.5309622365884</v>
+        <v>471.7887732684078</v>
       </c>
       <c r="D42" t="n">
-        <v>5.656878381327047</v>
+        <v>12.39906734950779</v>
       </c>
     </row>
     <row r="43">
@@ -6504,13 +6504,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>118.5309622365884</v>
+        <v>471.7887732684078</v>
       </c>
       <c r="C43" t="n">
-        <v>119.4518183192028</v>
+        <v>479.4518183192029</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9208560826143923</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="44">
@@ -6518,13 +6518,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>119.4518183192028</v>
+        <v>479.4518183192029</v>
       </c>
       <c r="C44" t="n">
-        <v>125.1086967005299</v>
+        <v>491.8508856687105</v>
       </c>
       <c r="D44" t="n">
-        <v>5.65687838132709</v>
+        <v>12.39906734950767</v>
       </c>
     </row>
     <row r="45">
@@ -6532,13 +6532,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>125.1086967005299</v>
+        <v>491.8508856687105</v>
       </c>
       <c r="C45" t="n">
-        <v>125.2731512047691</v>
+        <v>504.2499530182185</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1644545042392025</v>
+        <v>12.39906734950802</v>
       </c>
     </row>
     <row r="46">
@@ -6546,13 +6546,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>125.2731512047691</v>
+        <v>504.2499530182185</v>
       </c>
       <c r="C46" t="n">
-        <v>126.1940072873835</v>
+        <v>511.9129980690134</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9208560826143923</v>
+        <v>7.663045050794892</v>
       </c>
     </row>
     <row r="47">
@@ -6560,13 +6560,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>126.1940072873835</v>
+        <v>511.9129980690134</v>
       </c>
       <c r="C47" t="n">
-        <v>131.8508856687106</v>
+        <v>524.3120654185213</v>
       </c>
       <c r="D47" t="n">
-        <v>5.656878381327061</v>
+        <v>12.3990673495079</v>
       </c>
     </row>
     <row r="48">
@@ -6574,13 +6574,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>131.8508856687106</v>
+        <v>524.3120654185213</v>
       </c>
       <c r="C48" t="n">
-        <v>132.9361962555642</v>
+        <v>531.9751104693166</v>
       </c>
       <c r="D48" t="n">
-        <v>1.085310586853609</v>
+        <v>7.66304505079529</v>
       </c>
     </row>
     <row r="49">
@@ -6588,13 +6588,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>132.9361962555642</v>
+        <v>531.9751104693166</v>
       </c>
       <c r="C49" t="n">
-        <v>137.5077640500378</v>
+        <v>544.3741778188239</v>
       </c>
       <c r="D49" t="n">
-        <v>4.57156779447368</v>
+        <v>12.39906734950728</v>
       </c>
     </row>
     <row r="50">
@@ -6602,13 +6602,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>137.5077640500378</v>
+        <v>544.3741778188239</v>
       </c>
       <c r="C50" t="n">
-        <v>138.5930746368912</v>
+        <v>556.7732451683321</v>
       </c>
       <c r="D50" t="n">
-        <v>1.085310586853382</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="51">
@@ -6616,13 +6616,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>138.5930746368912</v>
+        <v>556.7732451683321</v>
       </c>
       <c r="C51" t="n">
-        <v>144.2499530182185</v>
+        <v>564.4362902191267</v>
       </c>
       <c r="D51" t="n">
-        <v>5.656878381327289</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="52">
@@ -6630,13 +6630,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>144.2499530182185</v>
+        <v>564.4362902191267</v>
       </c>
       <c r="C52" t="n">
-        <v>145.1708091008327</v>
+        <v>576.8353575686349</v>
       </c>
       <c r="D52" t="n">
-        <v>0.920856082614165</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="53">
@@ -6644,13 +6644,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>145.1708091008327</v>
+        <v>576.8353575686349</v>
       </c>
       <c r="C53" t="n">
-        <v>145.3352636050719</v>
+        <v>596.8974699689377</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1644545042392167</v>
+        <v>20.06211240030279</v>
       </c>
     </row>
     <row r="54">
@@ -6658,13 +6658,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>145.3352636050719</v>
+        <v>596.8974699689377</v>
       </c>
       <c r="C54" t="n">
-        <v>150.9921419863992</v>
+        <v>609.2965373184456</v>
       </c>
       <c r="D54" t="n">
-        <v>5.656878381327289</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="55">
@@ -6672,13 +6672,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>150.9921419863992</v>
+        <v>609.2965373184456</v>
       </c>
       <c r="C55" t="n">
-        <v>151.9129980690134</v>
+        <v>616.9595823692405</v>
       </c>
       <c r="D55" t="n">
-        <v>0.920856082614165</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="56">
@@ -6686,13 +6686,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>151.9129980690134</v>
+        <v>616.9595823692405</v>
       </c>
       <c r="C56" t="n">
-        <v>157.5698764503406</v>
+        <v>629.3586497187487</v>
       </c>
       <c r="D56" t="n">
-        <v>5.656878381327289</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="57">
@@ -6700,13 +6700,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>157.5698764503406</v>
+        <v>629.3586497187487</v>
       </c>
       <c r="C57" t="n">
-        <v>157.7343309545799</v>
+        <v>641.7577170682564</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="58">
@@ -6714,13 +6714,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>157.7343309545799</v>
+        <v>641.7577170682564</v>
       </c>
       <c r="C58" t="n">
-        <v>158.655187037194</v>
+        <v>649.4207621190513</v>
       </c>
       <c r="D58" t="n">
-        <v>0.920856082614165</v>
+        <v>7.663045050794949</v>
       </c>
     </row>
     <row r="59">
@@ -6728,13 +6728,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>158.655187037194</v>
+        <v>649.4207621190513</v>
       </c>
       <c r="C59" t="n">
-        <v>164.3120654185213</v>
+        <v>661.8198294685592</v>
       </c>
       <c r="D59" t="n">
-        <v>5.656878381327289</v>
+        <v>12.39906734950785</v>
       </c>
     </row>
     <row r="60">
@@ -6742,13 +6742,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>164.3120654185213</v>
+        <v>661.8198294685592</v>
       </c>
       <c r="C60" t="n">
-        <v>165.2329215011359</v>
+        <v>669.4828745193543</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9208560826146197</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="61">
@@ -6756,13 +6756,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>165.2329215011359</v>
+        <v>669.4828745193543</v>
       </c>
       <c r="C61" t="n">
-        <v>165.3973760053747</v>
+        <v>681.881941868862</v>
       </c>
       <c r="D61" t="n">
-        <v>0.164454504238762</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="62">
@@ -6770,13 +6770,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>165.3973760053747</v>
+        <v>681.881941868862</v>
       </c>
       <c r="C62" t="n">
-        <v>171.054254386702</v>
+        <v>694.2810092183699</v>
       </c>
       <c r="D62" t="n">
-        <v>5.656878381327289</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="63">
@@ -6784,13 +6784,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>171.054254386702</v>
+        <v>694.2810092183699</v>
       </c>
       <c r="C63" t="n">
-        <v>171.9751104693166</v>
+        <v>701.9440542691648</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9208560826146197</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="64">
@@ -6798,13 +6798,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>171.9751104693166</v>
+        <v>701.9440542691648</v>
       </c>
       <c r="C64" t="n">
-        <v>177.6319888506432</v>
+        <v>714.3431216186727</v>
       </c>
       <c r="D64" t="n">
-        <v>5.656878381326607</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="65">
@@ -6812,13 +6812,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>177.6319888506432</v>
+        <v>714.3431216186727</v>
       </c>
       <c r="C65" t="n">
-        <v>177.7964433548827</v>
+        <v>721.0853105868533</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1644545042394441</v>
+        <v>6.742188968180585</v>
       </c>
     </row>
     <row r="66">
@@ -6826,13 +6826,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>177.7964433548827</v>
+        <v>721.0853105868533</v>
       </c>
       <c r="C66" t="n">
-        <v>178.7172994374973</v>
+        <v>733.4843779363614</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9208560826146481</v>
+        <v>12.39906734950807</v>
       </c>
     </row>
     <row r="67">
@@ -6840,13 +6840,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>178.7172994374973</v>
+        <v>733.4843779363614</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3741778188239</v>
+        <v>741.1474229871559</v>
       </c>
       <c r="D67" t="n">
-        <v>5.656878381326578</v>
+        <v>7.663045050794494</v>
       </c>
     </row>
     <row r="68">
@@ -6854,13 +6854,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>184.3741778188239</v>
+        <v>741.1474229871559</v>
       </c>
       <c r="C68" t="n">
-        <v>185.4594884056779</v>
+        <v>753.5464903366641</v>
       </c>
       <c r="D68" t="n">
-        <v>1.085310586854064</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="69">
@@ -6868,13 +6868,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>185.4594884056779</v>
+        <v>753.5464903366641</v>
       </c>
       <c r="C69" t="n">
-        <v>190.0310562001514</v>
+        <v>761.2095353874588</v>
       </c>
       <c r="D69" t="n">
-        <v>4.571567794473452</v>
+        <v>7.663045050794722</v>
       </c>
     </row>
     <row r="70">
@@ -6882,13 +6882,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>190.0310562001514</v>
+        <v>761.2095353874588</v>
       </c>
       <c r="C70" t="n">
-        <v>191.1163667870046</v>
+        <v>773.6086027369669</v>
       </c>
       <c r="D70" t="n">
-        <v>1.085310586853154</v>
+        <v>12.39906734950807</v>
       </c>
     </row>
     <row r="71">
@@ -6896,13 +6896,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>191.1163667870046</v>
+        <v>773.6086027369669</v>
       </c>
       <c r="C71" t="n">
-        <v>196.7732451683321</v>
+        <v>786.0076700864748</v>
       </c>
       <c r="D71" t="n">
-        <v>5.656878381327516</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="72">
@@ -6910,13 +6910,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>196.7732451683321</v>
+        <v>786.0076700864748</v>
       </c>
       <c r="C72" t="n">
-        <v>197.694101250946</v>
+        <v>793.6707151372698</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9208560826139376</v>
+        <v>7.663045050794949</v>
       </c>
     </row>
     <row r="73">
@@ -6924,13 +6924,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>197.694101250946</v>
+        <v>793.6707151372698</v>
       </c>
       <c r="C73" t="n">
-        <v>197.8585557551852</v>
+        <v>806.0697824867776</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950785</v>
       </c>
     </row>
     <row r="74">
@@ -6938,13 +6938,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>197.8585557551852</v>
+        <v>806.0697824867776</v>
       </c>
       <c r="C74" t="n">
-        <v>203.5154341365127</v>
+        <v>826.1318948870806</v>
       </c>
       <c r="D74" t="n">
-        <v>5.656878381327516</v>
+        <v>20.06211240030302</v>
       </c>
     </row>
     <row r="75">
@@ -6952,13 +6952,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>203.5154341365127</v>
+        <v>826.1318948870806</v>
       </c>
       <c r="C75" t="n">
-        <v>204.4362902191267</v>
+        <v>838.5309622365884</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="76">
@@ -6966,13 +6966,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>204.4362902191267</v>
+        <v>838.5309622365884</v>
       </c>
       <c r="C76" t="n">
-        <v>210.0931686004542</v>
+        <v>846.1940072873836</v>
       </c>
       <c r="D76" t="n">
-        <v>5.656878381327516</v>
+        <v>7.663045050795176</v>
       </c>
     </row>
     <row r="77">
@@ -6980,13 +6980,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>210.0931686004542</v>
+        <v>846.1940072873836</v>
       </c>
       <c r="C77" t="n">
-        <v>210.2576231046934</v>
+        <v>858.5930746368913</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1644545042392167</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="78">
@@ -6994,13 +6994,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>210.2576231046934</v>
+        <v>858.5930746368913</v>
       </c>
       <c r="C78" t="n">
-        <v>211.1784791873073</v>
+        <v>870.9921419863992</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9208560826139376</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="79">
@@ -7008,13 +7008,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>211.1784791873073</v>
+        <v>870.9921419863992</v>
       </c>
       <c r="C79" t="n">
-        <v>216.8353575686349</v>
+        <v>878.655187037194</v>
       </c>
       <c r="D79" t="n">
-        <v>5.656878381327516</v>
+        <v>7.663045050794722</v>
       </c>
     </row>
     <row r="80">
@@ -7022,13 +7022,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>216.8353575686349</v>
+        <v>878.655187037194</v>
       </c>
       <c r="C80" t="n">
-        <v>217.920668155488</v>
+        <v>891.054254386702</v>
       </c>
       <c r="D80" t="n">
-        <v>1.085310586853154</v>
+        <v>12.39906734950807</v>
       </c>
     </row>
     <row r="81">
@@ -7036,13 +7036,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>217.920668155488</v>
+        <v>891.054254386702</v>
       </c>
       <c r="C81" t="n">
-        <v>223.5775465368156</v>
+        <v>898.7172994374972</v>
       </c>
       <c r="D81" t="n">
-        <v>5.656878381327545</v>
+        <v>7.663045050795176</v>
       </c>
     </row>
     <row r="82">
@@ -7050,13 +7050,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>223.5775465368156</v>
+        <v>898.7172994374972</v>
       </c>
       <c r="C82" t="n">
-        <v>230.155281000757</v>
+        <v>911.1163667870045</v>
       </c>
       <c r="D82" t="n">
-        <v>6.577734463941425</v>
+        <v>12.39906734950728</v>
       </c>
     </row>
     <row r="83">
@@ -7064,13 +7064,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>230.155281000757</v>
+        <v>911.1163667870045</v>
       </c>
       <c r="C83" t="n">
-        <v>230.3197355049962</v>
+        <v>923.5154341365128</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1644545042392451</v>
+        <v>12.3990673495083</v>
       </c>
     </row>
     <row r="84">
@@ -7078,13 +7078,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>230.3197355049962</v>
+        <v>923.5154341365128</v>
       </c>
       <c r="C84" t="n">
-        <v>236.8974699689377</v>
+        <v>931.1784791873074</v>
       </c>
       <c r="D84" t="n">
-        <v>6.577734463941454</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="85">
@@ -7092,13 +7092,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>236.8974699689377</v>
+        <v>931.1784791873074</v>
       </c>
       <c r="C85" t="n">
-        <v>242.5543483502649</v>
+        <v>943.5775465368156</v>
       </c>
       <c r="D85" t="n">
-        <v>5.65687838132726</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="86">
@@ -7106,13 +7106,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>242.5543483502649</v>
+        <v>943.5775465368156</v>
       </c>
       <c r="C86" t="n">
-        <v>243.6396589371183</v>
+        <v>963.6396589371184</v>
       </c>
       <c r="D86" t="n">
-        <v>1.085310586853353</v>
+        <v>20.06211240030279</v>
       </c>
     </row>
     <row r="87">
@@ -7120,13 +7120,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>243.6396589371183</v>
+        <v>963.6396589371184</v>
       </c>
       <c r="C87" t="n">
-        <v>249.2965373184456</v>
+        <v>976.0387262866263</v>
       </c>
       <c r="D87" t="n">
-        <v>5.656878381327317</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="88">
@@ -7134,13 +7134,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>249.2965373184456</v>
+        <v>976.0387262866263</v>
       </c>
       <c r="C88" t="n">
-        <v>250.2173934010598</v>
+        <v>983.7017713374211</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9208560826141934</v>
+        <v>7.663045050794722</v>
       </c>
     </row>
     <row r="89">
@@ -7148,13 +7148,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>250.2173934010598</v>
+        <v>983.7017713374211</v>
       </c>
       <c r="C89" t="n">
-        <v>250.381847905299</v>
+        <v>996.1008386869294</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1644545042391883</v>
+        <v>12.3990673495083</v>
       </c>
     </row>
     <row r="90">
@@ -7162,13 +7162,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>250.381847905299</v>
+        <v>996.1008386869294</v>
       </c>
       <c r="C90" t="n">
-        <v>256.0387262866263</v>
+        <v>1008.499906036437</v>
       </c>
       <c r="D90" t="n">
-        <v>5.656878381327289</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="91">
@@ -7176,13 +7176,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>256.0387262866263</v>
+        <v>1008.499906036437</v>
       </c>
       <c r="C91" t="n">
-        <v>256.9595823692405</v>
+        <v>1016.162951087232</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9208560826141934</v>
+        <v>7.663045050794949</v>
       </c>
     </row>
     <row r="92">
@@ -7190,13 +7190,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>256.9595823692405</v>
+        <v>1016.162951087232</v>
       </c>
       <c r="C92" t="n">
-        <v>262.616460750568</v>
+        <v>1028.56201843674</v>
       </c>
       <c r="D92" t="n">
-        <v>5.656878381327488</v>
+        <v>12.39906734950785</v>
       </c>
     </row>
     <row r="93">
@@ -7204,13 +7204,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>262.616460750568</v>
+        <v>1028.56201843674</v>
       </c>
       <c r="C93" t="n">
-        <v>262.780915254807</v>
+        <v>1036.225063487535</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1644545042390178</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="94">
@@ -7218,13 +7218,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>262.780915254807</v>
+        <v>1036.225063487535</v>
       </c>
       <c r="C94" t="n">
-        <v>263.7017713374211</v>
+        <v>1048.624130837043</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9208560826141365</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="95">
@@ -7232,13 +7232,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>263.7017713374211</v>
+        <v>1048.624130837043</v>
       </c>
       <c r="C95" t="n">
-        <v>269.3586497187487</v>
+        <v>1061.023198186551</v>
       </c>
       <c r="D95" t="n">
-        <v>5.656878381327545</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="96">
@@ -7246,13 +7246,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>269.3586497187487</v>
+        <v>1061.023198186551</v>
       </c>
       <c r="C96" t="n">
-        <v>270.4439603056018</v>
+        <v>1068.686243237345</v>
       </c>
       <c r="D96" t="n">
-        <v>1.085310586853154</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="97">
@@ -7260,13 +7260,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>270.4439603056018</v>
+        <v>1068.686243237345</v>
       </c>
       <c r="C97" t="n">
-        <v>275.0155281000757</v>
+        <v>1087.827499555034</v>
       </c>
       <c r="D97" t="n">
-        <v>4.571567794473879</v>
+        <v>19.14125631768866</v>
       </c>
     </row>
     <row r="98">
@@ -7274,13 +7274,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>275.0155281000757</v>
+        <v>1087.827499555034</v>
       </c>
       <c r="C98" t="n">
-        <v>276.1008386869293</v>
+        <v>1100.226566904542</v>
       </c>
       <c r="D98" t="n">
-        <v>1.085310586853609</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="99">
@@ -7288,13 +7288,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>276.1008386869293</v>
+        <v>1100.226566904542</v>
       </c>
       <c r="C99" t="n">
-        <v>281.7577170682564</v>
+        <v>1107.889611955337</v>
       </c>
       <c r="D99" t="n">
-        <v>5.65687838132709</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="100">
@@ -7302,13 +7302,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>281.7577170682564</v>
+        <v>1107.889611955337</v>
       </c>
       <c r="C100" t="n">
-        <v>282.6785731508708</v>
+        <v>1120.288679304845</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9208560826143639</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="101">
@@ -7316,13 +7316,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>282.6785731508708</v>
+        <v>1120.288679304845</v>
       </c>
       <c r="C101" t="n">
-        <v>282.84302765511</v>
+        <v>1127.951724355639</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1644545042392451</v>
+        <v>7.663045050794381</v>
       </c>
     </row>
     <row r="102">
@@ -7330,13 +7330,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>282.84302765511</v>
+        <v>1127.951724355639</v>
       </c>
       <c r="C102" t="n">
-        <v>288.499906036437</v>
+        <v>1140.350791705147</v>
       </c>
       <c r="D102" t="n">
-        <v>5.656878381327033</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="103">
@@ -7344,13 +7344,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>288.499906036437</v>
+        <v>1140.350791705147</v>
       </c>
       <c r="C103" t="n">
-        <v>289.4207621190515</v>
+        <v>1152.749859054656</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9208560826144208</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="104">
@@ -7358,13 +7358,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>289.4207621190515</v>
+        <v>1152.749859054656</v>
       </c>
       <c r="C104" t="n">
-        <v>295.0776405003785</v>
+        <v>1160.41290410545</v>
       </c>
       <c r="D104" t="n">
-        <v>5.656878381327033</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="105">
@@ -7372,13 +7372,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>295.0776405003785</v>
+        <v>1160.41290410545</v>
       </c>
       <c r="C105" t="n">
-        <v>295.2420950046177</v>
+        <v>1172.811971454958</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1644545042392451</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="106">
@@ -7386,13 +7386,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>295.2420950046177</v>
+        <v>1172.811971454958</v>
       </c>
       <c r="C106" t="n">
-        <v>296.1629510872321</v>
+        <v>1192.874083855261</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9208560826143639</v>
+        <v>20.06211240030325</v>
       </c>
     </row>
     <row r="107">
@@ -7400,13 +7400,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>296.1629510872321</v>
+        <v>1192.874083855261</v>
       </c>
       <c r="C107" t="n">
-        <v>301.8198294685592</v>
+        <v>1205.273151204769</v>
       </c>
       <c r="D107" t="n">
-        <v>5.65687838132709</v>
+        <v>12.3990673495075</v>
       </c>
     </row>
     <row r="108">
@@ -7414,13 +7414,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>301.8198294685592</v>
+        <v>1205.273151204769</v>
       </c>
       <c r="C108" t="n">
-        <v>302.7406855511736</v>
+        <v>1212.936196255564</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9208560826143639</v>
+        <v>7.66304505079529</v>
       </c>
     </row>
     <row r="109">
@@ -7428,13 +7428,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>302.7406855511736</v>
+        <v>1212.936196255564</v>
       </c>
       <c r="C109" t="n">
-        <v>302.9051400554128</v>
+        <v>1225.335263605072</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1644545042392451</v>
+        <v>12.3990673495075</v>
       </c>
     </row>
     <row r="110">
@@ -7442,13 +7442,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>302.9051400554128</v>
+        <v>1225.335263605072</v>
       </c>
       <c r="C110" t="n">
-        <v>308.5620184367398</v>
+        <v>1237.73433095458</v>
       </c>
       <c r="D110" t="n">
-        <v>5.656878381327033</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="111">
@@ -7456,13 +7456,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>308.5620184367398</v>
+        <v>1237.73433095458</v>
       </c>
       <c r="C111" t="n">
-        <v>309.4828745193543</v>
+        <v>1245.397376005375</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9208560826144208</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="112">
@@ -7470,13 +7470,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>309.4828745193543</v>
+        <v>1245.397376005375</v>
       </c>
       <c r="C112" t="n">
-        <v>315.1397529006813</v>
+        <v>1257.796443354883</v>
       </c>
       <c r="D112" t="n">
-        <v>5.656878381327033</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="113">
@@ -7484,13 +7484,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>315.1397529006813</v>
+        <v>1257.796443354883</v>
       </c>
       <c r="C113" t="n">
-        <v>315.3042074049205</v>
+        <v>1265.459488405678</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1644545042392451</v>
+        <v>7.663045050795517</v>
       </c>
     </row>
     <row r="114">
@@ -7498,13 +7498,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>315.3042074049205</v>
+        <v>1265.459488405678</v>
       </c>
       <c r="C114" t="n">
-        <v>316.2250634875349</v>
+        <v>1277.858555755185</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9208560826143639</v>
+        <v>12.39906734950705</v>
       </c>
     </row>
     <row r="115">
@@ -7512,13 +7512,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>316.2250634875349</v>
+        <v>1277.858555755185</v>
       </c>
       <c r="C115" t="n">
-        <v>321.881941868862</v>
+        <v>1290.257623104693</v>
       </c>
       <c r="D115" t="n">
-        <v>5.65687838132709</v>
+        <v>12.39906734950841</v>
       </c>
     </row>
     <row r="116">
@@ -7526,13 +7526,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>321.881941868862</v>
+        <v>1290.257623104693</v>
       </c>
       <c r="C116" t="n">
-        <v>322.9672524557156</v>
+        <v>1297.920668155488</v>
       </c>
       <c r="D116" t="n">
-        <v>1.085310586853609</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
     <row r="117">
@@ -7540,13 +7540,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>322.9672524557156</v>
+        <v>1297.920668155488</v>
       </c>
       <c r="C117" t="n">
-        <v>327.5388202501892</v>
+        <v>1310.319735504996</v>
       </c>
       <c r="D117" t="n">
-        <v>4.571567794473651</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="118">
@@ -7554,13 +7554,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>327.5388202501892</v>
+        <v>1310.319735504996</v>
       </c>
       <c r="C118" t="n">
-        <v>328.6241308370426</v>
+        <v>1330.381847905299</v>
       </c>
       <c r="D118" t="n">
-        <v>1.085310586853382</v>
+        <v>20.06211240030279</v>
       </c>
     </row>
     <row r="119">
@@ -7568,13 +7568,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>328.6241308370426</v>
+        <v>1330.381847905299</v>
       </c>
       <c r="C119" t="n">
-        <v>334.2810092183699</v>
+        <v>1342.780915254807</v>
       </c>
       <c r="D119" t="n">
-        <v>5.656878381327317</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="120">
@@ -7582,13 +7582,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>334.2810092183699</v>
+        <v>1342.780915254807</v>
       </c>
       <c r="C120" t="n">
-        <v>335.2018653009841</v>
+        <v>1350.443960305602</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9208560826141365</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="121">
@@ -7596,13 +7596,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>335.2018653009841</v>
+        <v>1350.443960305602</v>
       </c>
       <c r="C121" t="n">
-        <v>335.3663198052233</v>
+        <v>1362.84302765511</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1644545042392451</v>
+        <v>12.39906734950819</v>
       </c>
     </row>
     <row r="122">
@@ -7610,13 +7610,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>335.3663198052233</v>
+        <v>1362.84302765511</v>
       </c>
       <c r="C122" t="n">
-        <v>341.0231981865506</v>
+        <v>1375.242095004618</v>
       </c>
       <c r="D122" t="n">
-        <v>5.65687838132726</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="123">
@@ -7624,13 +7624,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>341.0231981865506</v>
+        <v>1375.242095004618</v>
       </c>
       <c r="C123" t="n">
-        <v>341.9440542691648</v>
+        <v>1382.905140055413</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9208560826141934</v>
+        <v>7.663045050795063</v>
       </c>
     </row>
     <row r="124">
@@ -7638,13 +7638,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>341.9440542691648</v>
+        <v>1382.905140055413</v>
       </c>
       <c r="C124" t="n">
-        <v>347.600932650492</v>
+        <v>1395.304207404921</v>
       </c>
       <c r="D124" t="n">
-        <v>5.65687838132726</v>
+        <v>12.39906734950773</v>
       </c>
     </row>
     <row r="125">
@@ -7652,13 +7652,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>347.600932650492</v>
+        <v>1395.304207404921</v>
       </c>
       <c r="C125" t="n">
-        <v>347.7653871547313</v>
+        <v>1402.967252455715</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1644545042392451</v>
+        <v>7.663045050794835</v>
       </c>
     </row>
     <row r="126">
@@ -7666,13 +7666,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>347.7653871547313</v>
+        <v>1402.967252455715</v>
       </c>
       <c r="C126" t="n">
-        <v>348.6862432373454</v>
+        <v>1415.366319805223</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9208560826141365</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="127">
@@ -7680,13 +7680,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>348.6862432373454</v>
+        <v>1415.366319805223</v>
       </c>
       <c r="C127" t="n">
-        <v>354.3431216186727</v>
+        <v>1427.765387154731</v>
       </c>
       <c r="D127" t="n">
-        <v>5.656878381327317</v>
+        <v>12.39906734950796</v>
       </c>
     </row>
     <row r="128">
@@ -7694,13 +7694,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>354.3431216186727</v>
+        <v>1427.765387154731</v>
       </c>
       <c r="C128" t="n">
-        <v>355.4284322055261</v>
+        <v>1435.428432205526</v>
       </c>
       <c r="D128" t="n">
-        <v>1.085310586853382</v>
+        <v>7.663045050794608</v>
       </c>
     </row>
   </sheetData>
